--- a/empirical/realized_shocks_Germany.xlsx
+++ b/empirical/realized_shocks_Germany.xlsx
@@ -88,9 +88,7 @@
       <c r="B2" s="1">
         <v>0.46521234512329102</v>
       </c>
-      <c r="C2" s="1">
-        <v>-0.18512357771396637</v>
-      </c>
+      <c r="C2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1">
@@ -100,7 +98,7 @@
         <v>0.53921568393707275</v>
       </c>
       <c r="C3" s="1">
-        <v>0.0092949206009507179</v>
+        <v>-0.2815743088722229</v>
       </c>
     </row>
     <row r="4">
@@ -111,7 +109,7 @@
         <v>0.018999595195055008</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.060344189405441284</v>
+        <v>-0.29623088240623474</v>
       </c>
     </row>
     <row r="5">
@@ -122,7 +120,7 @@
         <v>0.1291823536157608</v>
       </c>
       <c r="C5" s="1">
-        <v>0.32351648807525635</v>
+        <v>0.11323001235723495</v>
       </c>
     </row>
     <row r="6">
@@ -133,7 +131,7 @@
         <v>-0.43817660212516785</v>
       </c>
       <c r="C6" s="1">
-        <v>0.13064029812812805</v>
+        <v>-0.40514230728149414</v>
       </c>
     </row>
     <row r="7">
@@ -144,7 +142,7 @@
         <v>-0.015535296872258186</v>
       </c>
       <c r="C7" s="1">
-        <v>0.098331175744533539</v>
+        <v>-0.42916753888130188</v>
       </c>
     </row>
     <row r="8">
@@ -155,7 +153,7 @@
         <v>0.40162423253059387</v>
       </c>
       <c r="C8" s="1">
-        <v>0.55117899179458618</v>
+        <v>0.38730216026306152</v>
       </c>
     </row>
     <row r="9">
@@ -166,7 +164,7 @@
         <v>-0.28468817472457886</v>
       </c>
       <c r="C9" s="1">
-        <v>0.14162467420101166</v>
+        <v>0.32019150257110596</v>
       </c>
     </row>
     <row r="10">
@@ -177,7 +175,7 @@
         <v>-0.12352535873651505</v>
       </c>
       <c r="C10" s="1">
-        <v>0.18207831680774689</v>
+        <v>-0.29517686367034912</v>
       </c>
     </row>
     <row r="11">
@@ -188,7 +186,7 @@
         <v>0.38791996240615845</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.24100053310394287</v>
+        <v>-0.4761553704738617</v>
       </c>
     </row>
     <row r="12">
@@ -199,7 +197,7 @@
         <v>0.2667737603187561</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.09843011200428009</v>
+        <v>-0.020210681483149529</v>
       </c>
     </row>
     <row r="13">
@@ -210,7 +208,7 @@
         <v>0.00090988969895988703</v>
       </c>
       <c r="C13" s="1">
-        <v>0.15683571994304657</v>
+        <v>0.24756646156311035</v>
       </c>
     </row>
     <row r="14">
@@ -221,7 +219,7 @@
         <v>0.017355073243379593</v>
       </c>
       <c r="C14" s="1">
-        <v>-0.097753576934337616</v>
+        <v>-0.031152648851275444</v>
       </c>
     </row>
     <row r="15">
@@ -232,7 +230,7 @@
         <v>-0.038010384887456894</v>
       </c>
       <c r="C15" s="1">
-        <v>-0.20800955593585968</v>
+        <v>-0.71058034896850586</v>
       </c>
     </row>
     <row r="16">
@@ -243,7 +241,7 @@
         <v>0.1116408184170723</v>
       </c>
       <c r="C16" s="1">
-        <v>0.081002965569496155</v>
+        <v>0.1453314870595932</v>
       </c>
     </row>
     <row r="17">
@@ -254,7 +252,7 @@
         <v>-0.3564988374710083</v>
       </c>
       <c r="C17" s="1">
-        <v>0.023674065247178078</v>
+        <v>-0.1841757595539093</v>
       </c>
     </row>
     <row r="18">
@@ -265,7 +263,7 @@
         <v>-0.084605082869529724</v>
       </c>
       <c r="C18" s="1">
-        <v>0.074065782129764557</v>
+        <v>0.17301659286022186</v>
       </c>
     </row>
     <row r="19">
@@ -276,7 +274,7 @@
         <v>0.0041989265009760857</v>
       </c>
       <c r="C19" s="1">
-        <v>0.27045479416847229</v>
+        <v>0.34694951772689819</v>
       </c>
     </row>
     <row r="20">
@@ -287,7 +285,7 @@
         <v>-0.16957187652587891</v>
       </c>
       <c r="C20" s="1">
-        <v>0.51905298233032227</v>
+        <v>0.55668795108795166</v>
       </c>
     </row>
     <row r="21">
@@ -298,7 +296,7 @@
         <v>-0.071448929607868195</v>
       </c>
       <c r="C21" s="1">
-        <v>-0.35431262850761414</v>
+        <v>-0.55494779348373413</v>
       </c>
     </row>
     <row r="22">
@@ -309,7 +307,7 @@
         <v>0.039281997829675674</v>
       </c>
       <c r="C22" s="1">
-        <v>-0.098032265901565552</v>
+        <v>-0.31607496738433838</v>
       </c>
     </row>
     <row r="23">
@@ -320,7 +318,7 @@
         <v>-0.44365835189819336</v>
       </c>
       <c r="C23" s="1">
-        <v>0.035168815404176712</v>
+        <v>0.080637305974960327</v>
       </c>
     </row>
     <row r="24">
@@ -331,7 +329,7 @@
         <v>0.23881691694259644</v>
       </c>
       <c r="C24" s="1">
-        <v>0.0072431229054927826</v>
+        <v>0.062262572348117828</v>
       </c>
     </row>
     <row r="25">
@@ -339,10 +337,10 @@
         <v>197612</v>
       </c>
       <c r="B25" s="1">
-        <v>0.0047470987774431705</v>
+        <v>0.0047470987774431706</v>
       </c>
       <c r="C25" s="1">
-        <v>0.021644625812768936</v>
+        <v>-0.19428008794784546</v>
       </c>
     </row>
     <row r="26">
@@ -353,7 +351,7 @@
         <v>0.012969693168997765</v>
       </c>
       <c r="C26" s="1">
-        <v>0.032233733683824539</v>
+        <v>-0.15079586207866669</v>
       </c>
     </row>
     <row r="27">
@@ -364,7 +362,7 @@
         <v>-0.1657346785068512</v>
       </c>
       <c r="C27" s="1">
-        <v>0.1630517840385437</v>
+        <v>0.25261273980140686</v>
       </c>
     </row>
     <row r="28">
@@ -375,7 +373,7 @@
         <v>0.12808601558208466</v>
       </c>
       <c r="C28" s="1">
-        <v>-0.079121902585029602</v>
+        <v>-0.0012888435740023851</v>
       </c>
     </row>
     <row r="29">
@@ -386,7 +384,7 @@
         <v>0.34516245126724243</v>
       </c>
       <c r="C29" s="1">
-        <v>0.13765329122543335</v>
+        <v>-0.085518121719360352</v>
       </c>
     </row>
     <row r="30">
@@ -397,7 +395,7 @@
         <v>-0.15038582682609558</v>
       </c>
       <c r="C30" s="1">
-        <v>0.1762465238571167</v>
+        <v>0.24163521826267242</v>
       </c>
     </row>
     <row r="31">
@@ -408,7 +406,7 @@
         <v>-0.18930609524250031</v>
       </c>
       <c r="C31" s="1">
-        <v>-0.10566656291484833</v>
+        <v>-0.27123790979385376</v>
       </c>
     </row>
     <row r="32">
@@ -419,7 +417,7 @@
         <v>0.037637472152709961</v>
       </c>
       <c r="C32" s="1">
-        <v>0.44267758727073669</v>
+        <v>0.42822742462158203</v>
       </c>
     </row>
     <row r="33">
@@ -430,7 +428,7 @@
         <v>0.077654100954532623</v>
       </c>
       <c r="C33" s="1">
-        <v>-0.36521258950233459</v>
+        <v>-0.21578928828239441</v>
       </c>
     </row>
     <row r="34">
@@ -441,7 +439,7 @@
         <v>0.030511220917105675</v>
       </c>
       <c r="C34" s="1">
-        <v>0.070040807127952576</v>
+        <v>-0.10362815856933594</v>
       </c>
     </row>
     <row r="35">
@@ -452,7 +450,7 @@
         <v>0.10506273806095123</v>
       </c>
       <c r="C35" s="1">
-        <v>0.038562420755624771</v>
+        <v>0.081118211150169373</v>
       </c>
     </row>
     <row r="36">
@@ -463,7 +461,7 @@
         <v>0.0085843075066804886</v>
       </c>
       <c r="C36" s="1">
-        <v>0.0030122932512313128</v>
+        <v>0.061095356941223145</v>
       </c>
     </row>
     <row r="37">
@@ -474,7 +472,7 @@
         <v>-0.086249597370624542</v>
       </c>
       <c r="C37" s="1">
-        <v>-0.30112922191619873</v>
+        <v>-0.2639467716217041</v>
       </c>
     </row>
     <row r="38">
@@ -485,7 +483,7 @@
         <v>0.035992957651615143</v>
       </c>
       <c r="C38" s="1">
-        <v>0.26614761352539062</v>
+        <v>0.29444456100463867</v>
       </c>
     </row>
     <row r="39">
@@ -496,7 +494,7 @@
         <v>-0.0067645306698977947</v>
       </c>
       <c r="C39" s="1">
-        <v>0.33517274260520935</v>
+        <v>0.096082247793674469</v>
       </c>
     </row>
     <row r="40">
@@ -507,7 +505,7 @@
         <v>-0.04732932522892952</v>
       </c>
       <c r="C40" s="1">
-        <v>0.24330127239227295</v>
+        <v>0.27479448914527893</v>
       </c>
     </row>
     <row r="41">
@@ -518,7 +516,7 @@
         <v>-0.19478784501552582</v>
       </c>
       <c r="C41" s="1">
-        <v>-0.10911406576633453</v>
+        <v>0.01241720374673605</v>
       </c>
     </row>
     <row r="42">
@@ -529,7 +527,7 @@
         <v>0.075461402535438538</v>
       </c>
       <c r="C42" s="1">
-        <v>0.22468703985214233</v>
+        <v>0.36827307939529419</v>
       </c>
     </row>
     <row r="43">
@@ -540,7 +538,7 @@
         <v>0.06066073477268219</v>
       </c>
       <c r="C43" s="1">
-        <v>0.093801669776439667</v>
+        <v>0.15636077523231506</v>
       </c>
     </row>
     <row r="44">
@@ -551,7 +549,7 @@
         <v>0.14069397747516632</v>
       </c>
       <c r="C44" s="1">
-        <v>-0.005014792550355196</v>
+        <v>0.048228494822978973</v>
       </c>
     </row>
     <row r="45">
@@ -562,7 +560,7 @@
         <v>0.06066073477268219</v>
       </c>
       <c r="C45" s="1">
-        <v>-0.15097881853580475</v>
+        <v>-0.10190995782613754</v>
       </c>
     </row>
     <row r="46">
@@ -573,7 +571,7 @@
         <v>0.11876705288887024</v>
       </c>
       <c r="C46" s="1">
-        <v>0.12437321245670319</v>
+        <v>0.16980317234992981</v>
       </c>
     </row>
     <row r="47">
@@ -584,7 +582,7 @@
         <v>-0.15367487072944641</v>
       </c>
       <c r="C47" s="1">
-        <v>0.017084522172808647</v>
+        <v>-0.28152105212211609</v>
       </c>
     </row>
     <row r="48">
@@ -595,7 +593,7 @@
         <v>-0.11146555095911026</v>
       </c>
       <c r="C48" s="1">
-        <v>0.15220633149147034</v>
+        <v>0.31439375877380371</v>
       </c>
     </row>
     <row r="49">
@@ -606,7 +604,7 @@
         <v>-0.019372507929801941</v>
       </c>
       <c r="C49" s="1">
-        <v>-0.32987773418426514</v>
+        <v>-0.48301693797111511</v>
       </c>
     </row>
     <row r="50">
@@ -617,7 +615,7 @@
         <v>-0.012246260419487953</v>
       </c>
       <c r="C50" s="1">
-        <v>0.3197990357875824</v>
+        <v>0.35519534349441528</v>
       </c>
     </row>
     <row r="51">
@@ -628,7 +626,7 @@
         <v>-0.18492072820663452</v>
       </c>
       <c r="C51" s="1">
-        <v>0.16207200288772583</v>
+        <v>0.010690250433981419</v>
       </c>
     </row>
     <row r="52">
@@ -639,7 +637,7 @@
         <v>-0.10433930903673172</v>
       </c>
       <c r="C52" s="1">
-        <v>0.051854312419891357</v>
+        <v>-0.098790571093559265</v>
       </c>
     </row>
     <row r="53">
@@ -647,10 +645,10 @@
         <v>197904</v>
       </c>
       <c r="B53" s="1">
-        <v>-0.028691446408629417</v>
+        <v>-0.028691446408629418</v>
       </c>
       <c r="C53" s="1">
-        <v>-0.099789686501026154</v>
+        <v>-0.45233190059661865</v>
       </c>
     </row>
     <row r="54">
@@ -661,7 +659,7 @@
         <v>-0.28633269667625427</v>
       </c>
       <c r="C54" s="1">
-        <v>0.16845038533210754</v>
+        <v>0.28336584568023682</v>
       </c>
     </row>
     <row r="55">
@@ -672,7 +670,7 @@
         <v>-0.17286092042922974</v>
       </c>
       <c r="C55" s="1">
-        <v>-0.18202207982540131</v>
+        <v>-0.58736526966094971</v>
       </c>
     </row>
     <row r="56">
@@ -683,7 +681,7 @@
         <v>0.17358435690402985</v>
       </c>
       <c r="C56" s="1">
-        <v>-0.12181936204433441</v>
+        <v>-0.82480019330978394</v>
       </c>
     </row>
     <row r="57">
@@ -694,7 +692,7 @@
         <v>0.045311901718378067</v>
       </c>
       <c r="C57" s="1">
-        <v>0.25358095765113831</v>
+        <v>0.096374347805976868</v>
       </c>
     </row>
     <row r="58">
@@ -705,7 +703,7 @@
         <v>-0.018276162445545197</v>
       </c>
       <c r="C58" s="1">
-        <v>-0.017527451738715172</v>
+        <v>-0.19365334510803223</v>
       </c>
     </row>
     <row r="59">
@@ -716,7 +714,7 @@
         <v>-0.30222973227500916</v>
       </c>
       <c r="C59" s="1">
-        <v>0.2343142181634903</v>
+        <v>0.082563340663909912</v>
       </c>
     </row>
     <row r="60">
@@ -727,7 +725,7 @@
         <v>0.021192288026213646</v>
       </c>
       <c r="C60" s="1">
-        <v>-0.25546842813491821</v>
+        <v>-0.38771453499794006</v>
       </c>
     </row>
     <row r="61">
@@ -735,10 +733,10 @@
         <v>197912</v>
       </c>
       <c r="B61" s="1">
-        <v>-0.1026947870850563</v>
+        <v>-0.10269478708505631</v>
       </c>
       <c r="C61" s="1">
-        <v>-0.1705012321472168</v>
+        <v>-0.33055287599563599</v>
       </c>
     </row>
     <row r="62">
@@ -749,7 +747,7 @@
         <v>0.0020062336698174477</v>
       </c>
       <c r="C62" s="1">
-        <v>0.42232400178909302</v>
+        <v>0.46206176280975342</v>
       </c>
     </row>
     <row r="63">
@@ -760,7 +758,7 @@
         <v>0.081491298973560333</v>
       </c>
       <c r="C63" s="1">
-        <v>0.14297212660312653</v>
+        <v>-0.94211673736572266</v>
       </c>
     </row>
     <row r="64">
@@ -771,7 +769,7 @@
         <v>-0.43543574213981628</v>
       </c>
       <c r="C64" s="1">
-        <v>0.48664632439613342</v>
+        <v>0.22317877411842346</v>
       </c>
     </row>
     <row r="65">
@@ -782,7 +780,7 @@
         <v>0.13466407358646393</v>
       </c>
       <c r="C65" s="1">
-        <v>0.23128941655158997</v>
+        <v>0.34737241268157959</v>
       </c>
     </row>
     <row r="66">
@@ -793,7 +791,7 @@
         <v>0.12753783166408539</v>
       </c>
       <c r="C66" s="1">
-        <v>-0.10148843377828598</v>
+        <v>-0.54953223466873169</v>
       </c>
     </row>
     <row r="67">
@@ -804,7 +802,7 @@
         <v>0.10451456159353256</v>
       </c>
       <c r="C67" s="1">
-        <v>0.12281391769647598</v>
+        <v>-0.037854008376598358</v>
       </c>
     </row>
     <row r="68">
@@ -815,7 +813,7 @@
         <v>0.11986341327428818</v>
       </c>
       <c r="C68" s="1">
-        <v>-0.035156890749931335</v>
+        <v>0.060167890042066574</v>
       </c>
     </row>
     <row r="69">
@@ -826,7 +824,7 @@
         <v>-0.13887420296669006</v>
       </c>
       <c r="C69" s="1">
-        <v>0.18151779472827911</v>
+        <v>0.1092245951294899</v>
       </c>
     </row>
     <row r="70">
@@ -837,7 +835,7 @@
         <v>-0.023209717124700546</v>
       </c>
       <c r="C70" s="1">
-        <v>0.48311582207679749</v>
+        <v>0.56146681308746338</v>
       </c>
     </row>
     <row r="71">
@@ -848,7 +846,7 @@
         <v>-0.15531939268112183</v>
       </c>
       <c r="C71" s="1">
-        <v>0.15959261357784271</v>
+        <v>0.099395819008350372</v>
       </c>
     </row>
     <row r="72">
@@ -859,7 +857,7 @@
         <v>0.022288631647825241</v>
       </c>
       <c r="C72" s="1">
-        <v>0.067283675074577332</v>
+        <v>-0.19200620055198669</v>
       </c>
     </row>
     <row r="73">
@@ -870,7 +868,7 @@
         <v>-0.152030348777771</v>
       </c>
       <c r="C73" s="1">
-        <v>0.38255205750465393</v>
+        <v>-0.15918001532554627</v>
       </c>
     </row>
     <row r="74">
@@ -881,7 +879,7 @@
         <v>-0.14983765780925751</v>
       </c>
       <c r="C74" s="1">
-        <v>0.2305305153131485</v>
+        <v>-0.078103214502334595</v>
       </c>
     </row>
     <row r="75">
@@ -892,7 +890,7 @@
         <v>-0.012246260419487953</v>
       </c>
       <c r="C75" s="1">
-        <v>0.15840710699558258</v>
+        <v>-0.037716630846261978</v>
       </c>
     </row>
     <row r="76">
@@ -903,7 +901,7 @@
         <v>0.14672388136386871</v>
       </c>
       <c r="C76" s="1">
-        <v>0.036759708076715469</v>
+        <v>-0.79443317651748657</v>
       </c>
     </row>
     <row r="77">
@@ -914,7 +912,7 @@
         <v>0.23004615306854248</v>
       </c>
       <c r="C77" s="1">
-        <v>0.27485048770904541</v>
+        <v>-0.023759830743074417</v>
       </c>
     </row>
     <row r="78">
@@ -925,7 +923,7 @@
         <v>-0.18492072820663452</v>
       </c>
       <c r="C78" s="1">
-        <v>0.28781616687774658</v>
+        <v>0.30639037489891052</v>
       </c>
     </row>
     <row r="79">
@@ -936,7 +934,7 @@
         <v>0.29089334607124329</v>
       </c>
       <c r="C79" s="1">
-        <v>0.34022554755210876</v>
+        <v>0.28804543614387512</v>
       </c>
     </row>
     <row r="80">
@@ -947,7 +945,7 @@
         <v>0.022288631647825241</v>
       </c>
       <c r="C80" s="1">
-        <v>0.096761487424373627</v>
+        <v>-0.61355060338973999</v>
       </c>
     </row>
     <row r="81">
@@ -958,7 +956,7 @@
         <v>-0.152030348777771</v>
       </c>
       <c r="C81" s="1">
-        <v>0.19559931755065918</v>
+        <v>-0.069069035351276398</v>
       </c>
     </row>
     <row r="82">
@@ -969,7 +967,7 @@
         <v>-0.34443902969360352</v>
       </c>
       <c r="C82" s="1">
-        <v>-0.1599406898021698</v>
+        <v>-0.78284901380538941</v>
       </c>
     </row>
     <row r="83">
@@ -977,10 +975,10 @@
         <v>198110</v>
       </c>
       <c r="B83" s="1">
-        <v>-0.044040288776159286</v>
+        <v>-0.044040288776159287</v>
       </c>
       <c r="C83" s="1">
-        <v>-0.1617158055305481</v>
+        <v>-0.32416662573814392</v>
       </c>
     </row>
     <row r="84">
@@ -991,7 +989,7 @@
         <v>0.14288666844367981</v>
       </c>
       <c r="C84" s="1">
-        <v>0.099639743566513062</v>
+        <v>-0.24400657415390015</v>
       </c>
     </row>
     <row r="85">
@@ -1002,7 +1000,7 @@
         <v>-0.17724628746509552</v>
       </c>
       <c r="C85" s="1">
-        <v>0.28220304846763611</v>
+        <v>0.22862870991230011</v>
       </c>
     </row>
     <row r="86">
@@ -1013,7 +1011,7 @@
         <v>0.088069386780261993</v>
       </c>
       <c r="C86" s="1">
-        <v>0.088464207947254181</v>
+        <v>0.033968836069107056</v>
       </c>
     </row>
     <row r="87">
@@ -1024,7 +1022,7 @@
         <v>0.028318533673882484</v>
       </c>
       <c r="C87" s="1">
-        <v>0.3024456799030304</v>
+        <v>0.48620948195457459</v>
       </c>
     </row>
     <row r="88">
@@ -1035,7 +1033,7 @@
         <v>0.14014580845832825</v>
       </c>
       <c r="C88" s="1">
-        <v>0.2751612663269043</v>
+        <v>0.34650146961212158</v>
       </c>
     </row>
     <row r="89">
@@ -1046,7 +1044,7 @@
         <v>-0.064322687685489655</v>
       </c>
       <c r="C89" s="1">
-        <v>0.1492554098367691</v>
+        <v>0.29755374789237976</v>
       </c>
     </row>
     <row r="90">
@@ -1057,7 +1055,7 @@
         <v>-0.15477120876312256</v>
       </c>
       <c r="C90" s="1">
-        <v>-0.054891996085643768</v>
+        <v>-0.83912032842636108</v>
       </c>
     </row>
     <row r="91">
@@ -1068,7 +1066,7 @@
         <v>-0.19095061719417572</v>
       </c>
       <c r="C91" s="1">
-        <v>0.59919172525405884</v>
+        <v>-0.253682941198349</v>
       </c>
     </row>
     <row r="92">
@@ -1079,7 +1077,7 @@
         <v>-0.056648265570402145</v>
       </c>
       <c r="C92" s="1">
-        <v>0.53965741395950317</v>
+        <v>0.46295478940010071</v>
       </c>
     </row>
     <row r="93">
@@ -1090,7 +1088,7 @@
         <v>-0.081316046416759491</v>
       </c>
       <c r="C93" s="1">
-        <v>-0.12882936000823975</v>
+        <v>0.043159510940313339</v>
       </c>
     </row>
     <row r="94">
@@ -1101,7 +1099,7 @@
         <v>0.24758769571781158</v>
       </c>
       <c r="C94" s="1">
-        <v>0.14798732101917267</v>
+        <v>0.084532849490642548</v>
       </c>
     </row>
     <row r="95">
@@ -1112,7 +1110,7 @@
         <v>-0.067611724138259888</v>
       </c>
       <c r="C95" s="1">
-        <v>0.26352551579475403</v>
+        <v>-0.0037583978846669197</v>
       </c>
     </row>
     <row r="96">
@@ -1123,7 +1121,7 @@
         <v>0.066142462193965912</v>
       </c>
       <c r="C96" s="1">
-        <v>0.26013517379760742</v>
+        <v>0.19783006608486176</v>
       </c>
     </row>
     <row r="97">
@@ -1134,7 +1132,7 @@
         <v>0.27609267830848694</v>
       </c>
       <c r="C97" s="1">
-        <v>-0.22388637065887451</v>
+        <v>-0.1797933429479599</v>
       </c>
     </row>
     <row r="98">
@@ -1145,7 +1143,7 @@
         <v>-0.07035258412361145</v>
       </c>
       <c r="C98" s="1">
-        <v>0.15312463045120239</v>
+        <v>0.20430611073970795</v>
       </c>
     </row>
     <row r="99">
@@ -1156,7 +1154,7 @@
         <v>0.34296977519989014</v>
       </c>
       <c r="C99" s="1">
-        <v>0.50567835569381714</v>
+        <v>0.57114619016647339</v>
       </c>
     </row>
     <row r="100">
@@ -1167,7 +1165,7 @@
         <v>0.63185691833496094</v>
       </c>
       <c r="C100" s="1">
-        <v>0.07224215567111969</v>
+        <v>0.11632341891527176</v>
       </c>
     </row>
     <row r="101">
@@ -1178,7 +1176,7 @@
         <v>0.29747143387794495</v>
       </c>
       <c r="C101" s="1">
-        <v>-0.0060060429386794567</v>
+        <v>0.16224645078182221</v>
       </c>
     </row>
     <row r="102">
@@ -1189,7 +1187,7 @@
         <v>-0.3230603039264679</v>
       </c>
       <c r="C102" s="1">
-        <v>0.24357521533966064</v>
+        <v>0.20239312946796417</v>
       </c>
     </row>
     <row r="103">
@@ -1200,7 +1198,7 @@
         <v>0.23004615306854248</v>
       </c>
       <c r="C103" s="1">
-        <v>-0.19211344420909882</v>
+        <v>-0.16886298358440399</v>
       </c>
     </row>
     <row r="104">
@@ -1211,7 +1209,7 @@
         <v>0.0919065922498703</v>
       </c>
       <c r="C104" s="1">
-        <v>0.65905743837356567</v>
+        <v>0.37258890271186829</v>
       </c>
     </row>
     <row r="105">
@@ -1222,7 +1220,7 @@
         <v>-0.3564988374710083</v>
       </c>
       <c r="C105" s="1">
-        <v>0.1514894962310791</v>
+        <v>-0.23622600734233856</v>
       </c>
     </row>
     <row r="106">
@@ -1233,7 +1231,7 @@
         <v>0.10067736357450485</v>
       </c>
       <c r="C106" s="1">
-        <v>-0.23833054304122925</v>
+        <v>-0.27550411224365234</v>
       </c>
     </row>
     <row r="107">
@@ -1241,10 +1239,10 @@
         <v>198310</v>
       </c>
       <c r="B107" s="1">
-        <v>0.40272063016891479</v>
+        <v>0.4027206301689148</v>
       </c>
       <c r="C107" s="1">
-        <v>0.26343119144439697</v>
+        <v>0.26065433025360108</v>
       </c>
     </row>
     <row r="108">
@@ -1255,7 +1253,7 @@
         <v>0.039281997829675674</v>
       </c>
       <c r="C108" s="1">
-        <v>0.36147785186767578</v>
+        <v>0.48633092641830444</v>
       </c>
     </row>
     <row r="109">
@@ -1266,7 +1264,7 @@
         <v>0.051889963448047638</v>
       </c>
       <c r="C109" s="1">
-        <v>-0.050808101892471313</v>
+        <v>-0.0446278415620327</v>
       </c>
     </row>
     <row r="110">
@@ -1277,7 +1275,7 @@
         <v>0.15275378525257111</v>
       </c>
       <c r="C110" s="1">
-        <v>0.59308969974517822</v>
+        <v>0.67051434516906738</v>
       </c>
     </row>
     <row r="111">
@@ -1288,7 +1286,7 @@
         <v>-0.28304368257522583</v>
       </c>
       <c r="C111" s="1">
-        <v>-0.14871789515018463</v>
+        <v>-0.25181779265403748</v>
       </c>
     </row>
     <row r="112">
@@ -1299,7 +1297,7 @@
         <v>-0.0319804847240448</v>
       </c>
       <c r="C112" s="1">
-        <v>0.099630609154701233</v>
+        <v>0.16290612518787384</v>
       </c>
     </row>
     <row r="113">
@@ -1310,7 +1308,7 @@
         <v>-0.00018645422824192792</v>
       </c>
       <c r="C113" s="1">
-        <v>0.534187912940979</v>
+        <v>0.61298388242721558</v>
       </c>
     </row>
     <row r="114">
@@ -1321,7 +1319,7 @@
         <v>-0.24576790630817413</v>
       </c>
       <c r="C114" s="1">
-        <v>0.20111604034900665</v>
+        <v>0.43777480721473694</v>
       </c>
     </row>
     <row r="115">
@@ -1332,7 +1330,7 @@
         <v>0.066142462193965912</v>
       </c>
       <c r="C115" s="1">
-        <v>1.1479038000106812</v>
+        <v>0.99242764711380005</v>
       </c>
     </row>
     <row r="116">
@@ -1343,7 +1341,7 @@
         <v>-0.38007029891014099</v>
       </c>
       <c r="C116" s="1">
-        <v>-0.8223881721496582</v>
+        <v>-0.55955106019973755</v>
       </c>
     </row>
     <row r="117">
@@ -1354,7 +1352,7 @@
         <v>0.27061095833778381</v>
       </c>
       <c r="C117" s="1">
-        <v>0.5214005708694458</v>
+        <v>0.58296453952789307</v>
       </c>
     </row>
     <row r="118">
@@ -1365,7 +1363,7 @@
         <v>0.31775379180908203</v>
       </c>
       <c r="C118" s="1">
-        <v>0.0078084697015583515</v>
+        <v>0.25458851456642151</v>
       </c>
     </row>
     <row r="119">
@@ -1376,7 +1374,7 @@
         <v>0.059564393013715744</v>
       </c>
       <c r="C119" s="1">
-        <v>0.1871257871389389</v>
+        <v>-0.23969835042953491</v>
       </c>
     </row>
     <row r="120">
@@ -1387,7 +1385,7 @@
         <v>0.016258729621767998</v>
       </c>
       <c r="C120" s="1">
-        <v>-0.11804249137639999</v>
+        <v>-0.0035890261642634869</v>
       </c>
     </row>
     <row r="121">
@@ -1398,7 +1396,7 @@
         <v>0.050793621689081192</v>
       </c>
       <c r="C121" s="1">
-        <v>0.45829081535339355</v>
+        <v>0.58513939380645752</v>
       </c>
     </row>
     <row r="122">
@@ -1409,7 +1407,7 @@
         <v>0.17906609177589417</v>
       </c>
       <c r="C122" s="1">
-        <v>0.15423907339572906</v>
+        <v>0.14131444692611694</v>
       </c>
     </row>
     <row r="123">
@@ -1420,7 +1418,7 @@
         <v>0.047504588961601257</v>
       </c>
       <c r="C123" s="1">
-        <v>0.24156759679317474</v>
+        <v>0.26999968290328979</v>
       </c>
     </row>
     <row r="124">
@@ -1431,7 +1429,7 @@
         <v>0.035992957651615143</v>
       </c>
       <c r="C124" s="1">
-        <v>-0.022299749776721001</v>
+        <v>-0.25337821245193482</v>
       </c>
     </row>
     <row r="125">
@@ -1442,7 +1440,7 @@
         <v>0.16919897496700287</v>
       </c>
       <c r="C125" s="1">
-        <v>-0.088814482092857361</v>
+        <v>-0.069321736693382263</v>
       </c>
     </row>
     <row r="126">
@@ -1453,7 +1451,7 @@
         <v>0.50029540061950684</v>
       </c>
       <c r="C126" s="1">
-        <v>0.22320285439491272</v>
+        <v>0.29557600617408753</v>
       </c>
     </row>
     <row r="127">
@@ -1464,7 +1462,7 @@
         <v>0.28157439827919006</v>
       </c>
       <c r="C127" s="1">
-        <v>-0.14967237412929535</v>
+        <v>0.37398812174797058</v>
       </c>
     </row>
     <row r="128">
@@ -1475,7 +1473,7 @@
         <v>-0.31757855415344238</v>
       </c>
       <c r="C128" s="1">
-        <v>0.091507755219936371</v>
+        <v>0.077777333557605744</v>
       </c>
     </row>
     <row r="129">
@@ -1486,7 +1484,7 @@
         <v>0.47288674116134644</v>
       </c>
       <c r="C129" s="1">
-        <v>0.43717929720878601</v>
+        <v>0.37847229838371277</v>
       </c>
     </row>
     <row r="130">
@@ -1497,7 +1495,7 @@
         <v>0.28431528806686401</v>
       </c>
       <c r="C130" s="1">
-        <v>-0.011187182739377022</v>
+        <v>0.17911083996295929</v>
       </c>
     </row>
     <row r="131">
@@ -1508,7 +1506,7 @@
         <v>0.65926557779312134</v>
       </c>
       <c r="C131" s="1">
-        <v>-0.12416033446788788</v>
+        <v>-0.19675499200820923</v>
       </c>
     </row>
     <row r="132">
@@ -1519,7 +1517,7 @@
         <v>-0.17395725846290588</v>
       </c>
       <c r="C132" s="1">
-        <v>-0.19330398738384247</v>
+        <v>-0.24613738059997559</v>
       </c>
     </row>
     <row r="133">
@@ -1530,7 +1528,7 @@
         <v>0.6307605504989624</v>
       </c>
       <c r="C133" s="1">
-        <v>0.31737017631530762</v>
+        <v>0.36323150992393494</v>
       </c>
     </row>
     <row r="134">
@@ -1541,7 +1539,7 @@
         <v>-0.024854235351085663</v>
       </c>
       <c r="C134" s="1">
-        <v>-0.26240602135658264</v>
+        <v>0.25330615043640137</v>
       </c>
     </row>
     <row r="135">
@@ -1552,7 +1550,7 @@
         <v>-0.1361333429813385</v>
       </c>
       <c r="C135" s="1">
-        <v>-0.13573260605335236</v>
+        <v>0.33698287606239319</v>
       </c>
     </row>
     <row r="136">
@@ -1563,7 +1561,7 @@
         <v>0.45753791928291321</v>
       </c>
       <c r="C136" s="1">
-        <v>-0.11727593839168549</v>
+        <v>0.36438795924186707</v>
       </c>
     </row>
     <row r="137">
@@ -1574,7 +1572,7 @@
         <v>0.23169068992137909</v>
       </c>
       <c r="C137" s="1">
-        <v>0.022018969058990479</v>
+        <v>0.57532870769500732</v>
       </c>
     </row>
     <row r="138">
@@ -1585,7 +1583,7 @@
         <v>-0.55055207014083862</v>
       </c>
       <c r="C138" s="1">
-        <v>0.46514350175857544</v>
+        <v>0.48940300941467285</v>
       </c>
     </row>
     <row r="139">
@@ -1596,7 +1594,7 @@
         <v>-0.1322961151599884</v>
       </c>
       <c r="C139" s="1">
-        <v>0.35215681791305542</v>
+        <v>0.42320463061332703</v>
       </c>
     </row>
     <row r="140">
@@ -1607,7 +1605,7 @@
         <v>-0.42008692026138306</v>
       </c>
       <c r="C140" s="1">
-        <v>-0.19467905163764954</v>
+        <v>0.31098201870918274</v>
       </c>
     </row>
     <row r="141">
@@ -1618,7 +1616,7 @@
         <v>0.78863435983657837</v>
       </c>
       <c r="C141" s="1">
-        <v>0.023381074890494347</v>
+        <v>0.45921963453292847</v>
       </c>
     </row>
     <row r="142">
@@ -1629,7 +1627,7 @@
         <v>-0.36746230721473694</v>
       </c>
       <c r="C142" s="1">
-        <v>0.13953366875648499</v>
+        <v>0.27400001883506775</v>
       </c>
     </row>
     <row r="143">
@@ -1640,7 +1638,7 @@
         <v>0.047504588961601257</v>
       </c>
       <c r="C143" s="1">
-        <v>-0.02870791032910347</v>
+        <v>0.68564534187316895</v>
       </c>
     </row>
     <row r="144">
@@ -1651,7 +1649,7 @@
         <v>0.19715577363967896</v>
       </c>
       <c r="C144" s="1">
-        <v>0.27740678191184998</v>
+        <v>0.35835081338882446</v>
       </c>
     </row>
     <row r="145">
@@ -1662,7 +1660,7 @@
         <v>-0.086249597370624542</v>
       </c>
       <c r="C145" s="1">
-        <v>0.46055877208709717</v>
+        <v>0.4754825234413147</v>
       </c>
     </row>
     <row r="146">
@@ -1673,7 +1671,7 @@
         <v>-0.63442248106002808</v>
       </c>
       <c r="C146" s="1">
-        <v>0.052277497947216034</v>
+        <v>0.086037896573543549</v>
       </c>
     </row>
     <row r="147">
@@ -1684,7 +1682,7 @@
         <v>-0.31154865026473999</v>
       </c>
       <c r="C147" s="1">
-        <v>0.11119425296783447</v>
+        <v>0.16517168283462525</v>
       </c>
     </row>
     <row r="148">
@@ -1692,10 +1690,10 @@
         <v>198703</v>
       </c>
       <c r="B148" s="1">
-        <v>0.17632520198822021</v>
+        <v>0.17632520198822022</v>
       </c>
       <c r="C148" s="1">
-        <v>0.14888514578342438</v>
+        <v>0.29864290356636047</v>
       </c>
     </row>
     <row r="149">
@@ -1706,7 +1704,7 @@
         <v>-0.016083469614386559</v>
       </c>
       <c r="C149" s="1">
-        <v>-0.12567226588726044</v>
+        <v>0.019807983189821243</v>
       </c>
     </row>
     <row r="150">
@@ -1717,7 +1715,7 @@
         <v>-0.11639910936355591</v>
       </c>
       <c r="C150" s="1">
-        <v>0.16566388309001923</v>
+        <v>0.21501763164997101</v>
       </c>
     </row>
     <row r="151">
@@ -1728,7 +1726,7 @@
         <v>0.32268738746643066</v>
       </c>
       <c r="C151" s="1">
-        <v>0.33279159665107727</v>
+        <v>0.49160712957382202</v>
       </c>
     </row>
     <row r="152">
@@ -1739,7 +1737,7 @@
         <v>0.31117573380470276</v>
       </c>
       <c r="C152" s="1">
-        <v>0.25041630864143372</v>
+        <v>0.41259253025054932</v>
       </c>
     </row>
     <row r="153">
@@ -1750,7 +1748,7 @@
         <v>0.038185644894838333</v>
       </c>
       <c r="C153" s="1">
-        <v>-0.14468513429164886</v>
+        <v>0.041347712278366089</v>
       </c>
     </row>
     <row r="154">
@@ -1761,7 +1759,7 @@
         <v>-0.17286092042922974</v>
       </c>
       <c r="C154" s="1">
-        <v>0.14404834806919098</v>
+        <v>0.63746494054794312</v>
       </c>
     </row>
     <row r="155">
@@ -1772,7 +1770,7 @@
         <v>-1.2423461675643921</v>
       </c>
       <c r="C155" s="1">
-        <v>0.31312176585197449</v>
+        <v>0.4076114296913147</v>
       </c>
     </row>
     <row r="156">
@@ -1783,7 +1781,7 @@
         <v>-0.76488763093948364</v>
       </c>
       <c r="C156" s="1">
-        <v>-0.18033364415168762</v>
+        <v>-0.11977718025445938</v>
       </c>
     </row>
     <row r="157">
@@ -1794,7 +1792,7 @@
         <v>-0.12900708615779877</v>
       </c>
       <c r="C157" s="1">
-        <v>-0.033305652439594269</v>
+        <v>0.074693284928798676</v>
       </c>
     </row>
     <row r="158">
@@ -1805,7 +1803,7 @@
         <v>-0.38884103298187256</v>
       </c>
       <c r="C158" s="1">
-        <v>0.52659434080123901</v>
+        <v>0.60914057493209839</v>
       </c>
     </row>
     <row r="159">
@@ -1813,10 +1811,10 @@
         <v>198802</v>
       </c>
       <c r="B159" s="1">
-        <v>0.82371747493743896</v>
+        <v>0.82371747493743897</v>
       </c>
       <c r="C159" s="1">
-        <v>0.018411682918667793</v>
+        <v>0.20805664360523224</v>
       </c>
     </row>
     <row r="160">
@@ -1827,7 +1825,7 @@
         <v>-0.075834318995475769</v>
       </c>
       <c r="C160" s="1">
-        <v>0.39372697472572327</v>
+        <v>0.42672041058540344</v>
       </c>
     </row>
     <row r="161">
@@ -1838,7 +1836,7 @@
         <v>-0.11201372742652893</v>
       </c>
       <c r="C161" s="1">
-        <v>0.00096592033514752984</v>
+        <v>0.15820500254631043</v>
       </c>
     </row>
     <row r="162">
@@ -1849,7 +1847,7 @@
         <v>0.076557755470275879</v>
       </c>
       <c r="C162" s="1">
-        <v>0.13180212676525116</v>
+        <v>0.11515996605157852</v>
       </c>
     </row>
     <row r="163">
@@ -1860,7 +1858,7 @@
         <v>0.18783684074878693</v>
       </c>
       <c r="C163" s="1">
-        <v>0.30404898524284363</v>
+        <v>0.43893742561340332</v>
       </c>
     </row>
     <row r="164">
@@ -1871,7 +1869,7 @@
         <v>0.11712253838777542</v>
       </c>
       <c r="C164" s="1">
-        <v>0.55294317007064819</v>
+        <v>0.77248638868331909</v>
       </c>
     </row>
     <row r="165">
@@ -1882,7 +1880,7 @@
         <v>-0.048973843455314636</v>
       </c>
       <c r="C165" s="1">
-        <v>-0.28516259789466858</v>
+        <v>-0.04390445351600647</v>
       </c>
     </row>
     <row r="166">
@@ -1893,7 +1891,7 @@
         <v>0.31720566749572754</v>
       </c>
       <c r="C166" s="1">
-        <v>0.13949926197528839</v>
+        <v>0.25611862540245056</v>
       </c>
     </row>
     <row r="167">
@@ -1904,7 +1902,7 @@
         <v>0.17029532790184021</v>
       </c>
       <c r="C167" s="1">
-        <v>-0.080392941832542419</v>
+        <v>0.032586749643087387</v>
       </c>
     </row>
     <row r="168">
@@ -1915,7 +1913,7 @@
         <v>-0.20136590301990509</v>
       </c>
       <c r="C168" s="1">
-        <v>-0.11392471194267273</v>
+        <v>-0.20949019491672516</v>
       </c>
     </row>
     <row r="169">
@@ -1926,7 +1924,7 @@
         <v>0.20702289044857025</v>
       </c>
       <c r="C169" s="1">
-        <v>-0.17963331937789917</v>
+        <v>-0.19036248326301575</v>
       </c>
     </row>
     <row r="170">
@@ -1937,7 +1935,7 @@
         <v>0.03270392119884491</v>
       </c>
       <c r="C170" s="1">
-        <v>0.4300825297832489</v>
+        <v>0.26883015036582947</v>
       </c>
     </row>
     <row r="171">
@@ -1948,7 +1946,7 @@
         <v>-0.17669811844825745</v>
       </c>
       <c r="C171" s="1">
-        <v>0.19261406362056732</v>
+        <v>0.18245896697044373</v>
       </c>
     </row>
     <row r="172">
@@ -1959,7 +1957,7 @@
         <v>0.077654100954532623</v>
       </c>
       <c r="C172" s="1">
-        <v>0.020978780463337898</v>
+        <v>0.19913089275360108</v>
       </c>
     </row>
     <row r="173">
@@ -1970,7 +1968,7 @@
         <v>0.17139166593551636</v>
       </c>
       <c r="C173" s="1">
-        <v>-0.27097901701927185</v>
+        <v>-0.45872089266777039</v>
       </c>
     </row>
     <row r="174">
@@ -1981,7 +1979,7 @@
         <v>0.062305252999067307</v>
       </c>
       <c r="C174" s="1">
-        <v>0.80909973382949829</v>
+        <v>0.99692755937576294</v>
       </c>
     </row>
     <row r="175">
@@ -1992,7 +1990,7 @@
         <v>0.20647473633289337</v>
       </c>
       <c r="C175" s="1">
-        <v>-0.3333161473274231</v>
+        <v>-0.10893621295690537</v>
       </c>
     </row>
     <row r="176">
@@ -2003,7 +2001,7 @@
         <v>0.22127540409564972</v>
       </c>
       <c r="C176" s="1">
-        <v>-0.1879694014787674</v>
+        <v>-0.10514079034328461</v>
       </c>
     </row>
     <row r="177">
@@ -2014,7 +2012,7 @@
         <v>0.17577706277370453</v>
       </c>
       <c r="C177" s="1">
-        <v>0.46303281188011169</v>
+        <v>0.54292356967926025</v>
       </c>
     </row>
     <row r="178">
@@ -2025,7 +2023,7 @@
         <v>-0.017727987840771675</v>
       </c>
       <c r="C178" s="1">
-        <v>0.073722727596759796</v>
+        <v>0.074708960950374603</v>
       </c>
     </row>
     <row r="179">
@@ -2036,7 +2034,7 @@
         <v>-0.41570150852203369</v>
       </c>
       <c r="C179" s="1">
-        <v>-0.079573936760425568</v>
+        <v>-0.35328495502471924</v>
       </c>
     </row>
     <row r="180">
@@ -2047,7 +2045,7 @@
         <v>0.29911595582962036</v>
       </c>
       <c r="C180" s="1">
-        <v>0.21004435420036316</v>
+        <v>0.22724394500255585</v>
       </c>
     </row>
     <row r="181">
@@ -2058,7 +2056,7 @@
         <v>0.63240504264831543</v>
       </c>
       <c r="C181" s="1">
-        <v>-0.38492119312286377</v>
+        <v>-0.68058621883392334</v>
       </c>
     </row>
     <row r="182">
@@ -2069,7 +2067,7 @@
         <v>0.10451456159353256</v>
       </c>
       <c r="C182" s="1">
-        <v>-0.028277372941374779</v>
+        <v>-0.10509882867336273</v>
       </c>
     </row>
     <row r="183">
@@ -2080,7 +2078,7 @@
         <v>-0.068708069622516632</v>
       </c>
       <c r="C183" s="1">
-        <v>0.1021411120891571</v>
+        <v>0.24754555523395538</v>
       </c>
     </row>
     <row r="184">
@@ -2091,7 +2089,7 @@
         <v>0.48604285717010498</v>
       </c>
       <c r="C184" s="1">
-        <v>-0.0088356193155050278</v>
+        <v>0.18340077996253967</v>
       </c>
     </row>
     <row r="185">
@@ -2102,7 +2100,7 @@
         <v>-0.44639921188354492</v>
       </c>
       <c r="C185" s="1">
-        <v>0.2921949028968811</v>
+        <v>0.43459531664848328</v>
       </c>
     </row>
     <row r="186">
@@ -2113,7 +2111,7 @@
         <v>0.052986316382884979</v>
       </c>
       <c r="C186" s="1">
-        <v>-0.28068044781684875</v>
+        <v>-0.11848289519548416</v>
       </c>
     </row>
     <row r="187">
@@ -2124,7 +2122,7 @@
         <v>0.082039475440979004</v>
       </c>
       <c r="C187" s="1">
-        <v>0.13047434389591217</v>
+        <v>0.31760215759277344</v>
       </c>
     </row>
     <row r="188">
@@ -2135,7 +2133,7 @@
         <v>0.13685676455497742</v>
       </c>
       <c r="C188" s="1">
-        <v>0.1428152471780777</v>
+        <v>0.15758976340293884</v>
       </c>
     </row>
     <row r="189">
@@ -2146,7 +2144,7 @@
         <v>-0.85533612966537476</v>
       </c>
       <c r="C189" s="1">
-        <v>-0.066325046122074127</v>
+        <v>-0.49681323766708374</v>
       </c>
     </row>
     <row r="190">
@@ -2157,7 +2155,7 @@
         <v>-0.98799401521682739</v>
       </c>
       <c r="C190" s="1">
-        <v>0.085666470229625702</v>
+        <v>-0.077450960874557495</v>
       </c>
     </row>
     <row r="191">
@@ -2168,7 +2166,7 @@
         <v>0.4520561695098877</v>
       </c>
       <c r="C191" s="1">
-        <v>-0.10754069685935974</v>
+        <v>-0.72681909799575806</v>
       </c>
     </row>
     <row r="192">
@@ -2179,7 +2177,7 @@
         <v>-0.015535296872258186</v>
       </c>
       <c r="C192" s="1">
-        <v>-0.018858697265386581</v>
+        <v>0.46820339560508728</v>
       </c>
     </row>
     <row r="193">
@@ -2190,7 +2188,7 @@
         <v>-0.21507023274898529</v>
       </c>
       <c r="C193" s="1">
-        <v>0.07401970773935318</v>
+        <v>0.25873842835426331</v>
       </c>
     </row>
     <row r="194">
@@ -2201,7 +2199,7 @@
         <v>-0.01663164421916008</v>
       </c>
       <c r="C194" s="1">
-        <v>-0.21486303210258484</v>
+        <v>-0.17308174073696137</v>
       </c>
     </row>
     <row r="195">
@@ -2212,7 +2210,7 @@
         <v>0.47453129291534424</v>
       </c>
       <c r="C195" s="1">
-        <v>-0.35927435755729675</v>
+        <v>-0.32264804840087891</v>
       </c>
     </row>
     <row r="196">
@@ -2223,7 +2221,7 @@
         <v>-0.17176458239555359</v>
       </c>
       <c r="C196" s="1">
-        <v>0.07322363555431366</v>
+        <v>0.10296670347452164</v>
       </c>
     </row>
     <row r="197">
@@ -2234,7 +2232,7 @@
         <v>0.23991325497627258</v>
       </c>
       <c r="C197" s="1">
-        <v>0.12067695707082748</v>
+        <v>0.11768205463886261</v>
       </c>
     </row>
     <row r="198">
@@ -2245,7 +2243,7 @@
         <v>0.22730530798435211</v>
       </c>
       <c r="C198" s="1">
-        <v>-0.23216243088245392</v>
+        <v>-0.20265309512615204</v>
       </c>
     </row>
     <row r="199">
@@ -2256,7 +2254,7 @@
         <v>-0.30168154835700989</v>
       </c>
       <c r="C199" s="1">
-        <v>0.38403201103210449</v>
+        <v>0.30513677000999451</v>
       </c>
     </row>
     <row r="200">
@@ -2267,7 +2265,7 @@
         <v>-0.072545275092124939</v>
       </c>
       <c r="C200" s="1">
-        <v>-0.56079941987991333</v>
+        <v>-0.67924022674560547</v>
       </c>
     </row>
     <row r="201">
@@ -2278,7 +2276,7 @@
         <v>0.031607575714588165</v>
       </c>
       <c r="C201" s="1">
-        <v>-0.48821428418159485</v>
+        <v>-0.4275122880935669</v>
       </c>
     </row>
     <row r="202">
@@ -2286,10 +2284,10 @@
         <v>199109</v>
       </c>
       <c r="B202" s="1">
-        <v>-0.19807687401771545</v>
+        <v>-0.19807687401771546</v>
       </c>
       <c r="C202" s="1">
-        <v>-0.42848679423332214</v>
+        <v>-0.34584954380989075</v>
       </c>
     </row>
     <row r="203">
@@ -2300,7 +2298,7 @@
         <v>-0.1224290132522583</v>
       </c>
       <c r="C203" s="1">
-        <v>-0.13140015304088593</v>
+        <v>-0.079094178974628449</v>
       </c>
     </row>
     <row r="204">
@@ -2311,7 +2309,7 @@
         <v>-0.10653200000524521</v>
       </c>
       <c r="C204" s="1">
-        <v>-0.35499143600463867</v>
+        <v>-0.34112170338630676</v>
       </c>
     </row>
     <row r="205">
@@ -2322,7 +2320,7 @@
         <v>-0.058292783796787262</v>
       </c>
       <c r="C205" s="1">
-        <v>-0.44267180562019348</v>
+        <v>-0.34074941277503967</v>
       </c>
     </row>
     <row r="206">
@@ -2330,10 +2328,10 @@
         <v>199201</v>
       </c>
       <c r="B206" s="1">
-        <v>0.33968076109886169</v>
+        <v>0.3396807610988617</v>
       </c>
       <c r="C206" s="1">
-        <v>0.039583876729011536</v>
+        <v>0.039230499416589737</v>
       </c>
     </row>
     <row r="207">
@@ -2344,7 +2342,7 @@
         <v>0.18290328979492188</v>
       </c>
       <c r="C207" s="1">
-        <v>0.018278373405337334</v>
+        <v>-0.015430212952196598</v>
       </c>
     </row>
     <row r="208">
@@ -2355,7 +2353,7 @@
         <v>-0.12078449875116348</v>
       </c>
       <c r="C208" s="1">
-        <v>-0.41206079721450806</v>
+        <v>-0.35114538669586182</v>
       </c>
     </row>
     <row r="209">
@@ -2366,7 +2364,7 @@
         <v>-0.03691403940320015</v>
       </c>
       <c r="C209" s="1">
-        <v>-0.31282755732536316</v>
+        <v>-0.27942097187042236</v>
       </c>
     </row>
     <row r="210">
@@ -2377,7 +2375,7 @@
         <v>0.11821888387203217</v>
       </c>
       <c r="C210" s="1">
-        <v>-0.42767316102981567</v>
+        <v>-0.33333864808082581</v>
       </c>
     </row>
     <row r="211">
@@ -2388,7 +2386,7 @@
         <v>-0.23425628244876862</v>
       </c>
       <c r="C211" s="1">
-        <v>-0.54167735576629639</v>
+        <v>-0.43531319499015808</v>
       </c>
     </row>
     <row r="212">
@@ -2399,7 +2397,7 @@
         <v>-0.47325965762138367</v>
       </c>
       <c r="C212" s="1">
-        <v>-0.63878059387207031</v>
+        <v>-0.53028523921966553</v>
       </c>
     </row>
     <row r="213">
@@ -2410,7 +2408,7 @@
         <v>-0.31428951025009155</v>
       </c>
       <c r="C213" s="1">
-        <v>-0.50514262914657593</v>
+        <v>-0.40068015456199646</v>
       </c>
     </row>
     <row r="214">
@@ -2421,7 +2419,7 @@
         <v>-0.23041906952857971</v>
       </c>
       <c r="C214" s="1">
-        <v>-0.31921696662902832</v>
+        <v>-0.22602149844169617</v>
       </c>
     </row>
     <row r="215">
@@ -2432,7 +2430,7 @@
         <v>0.039830170571804047</v>
       </c>
       <c r="C215" s="1">
-        <v>-0.1463838517665863</v>
+        <v>-0.11781950294971466</v>
       </c>
     </row>
     <row r="216">
@@ -2443,7 +2441,7 @@
         <v>0.10396639257669449</v>
       </c>
       <c r="C216" s="1">
-        <v>-0.048076432198286057</v>
+        <v>-0.056690853089094162</v>
       </c>
     </row>
     <row r="217">
@@ -2454,7 +2452,7 @@
         <v>-0.065419033169746399</v>
       </c>
       <c r="C217" s="1">
-        <v>-0.43212524056434631</v>
+        <v>-0.32599195837974548</v>
       </c>
     </row>
     <row r="218">
@@ -2465,7 +2463,7 @@
         <v>0.08423217386007309</v>
       </c>
       <c r="C218" s="1">
-        <v>-0.25057107210159302</v>
+        <v>-0.25154292583465576</v>
       </c>
     </row>
     <row r="219">
@@ -2476,7 +2474,7 @@
         <v>0.34187343716621399</v>
       </c>
       <c r="C219" s="1">
-        <v>-0.34366831183433533</v>
+        <v>-0.3167700469493866</v>
       </c>
     </row>
     <row r="220">
@@ -2487,7 +2485,7 @@
         <v>0.015162386000156403</v>
       </c>
       <c r="C220" s="1">
-        <v>-0.20353206992149353</v>
+        <v>-0.18889313936233521</v>
       </c>
     </row>
     <row r="221">
@@ -2498,7 +2496,7 @@
         <v>-0.19862504303455353</v>
       </c>
       <c r="C221" s="1">
-        <v>-0.29706040024757385</v>
+        <v>-0.23767946660518646</v>
       </c>
     </row>
     <row r="222">
@@ -2509,7 +2507,7 @@
         <v>-0.030884137377142906</v>
       </c>
       <c r="C222" s="1">
-        <v>-0.19784289598464966</v>
+        <v>-0.13479973375797272</v>
       </c>
     </row>
     <row r="223">
@@ -2520,7 +2518,7 @@
         <v>0.11109264940023422</v>
       </c>
       <c r="C223" s="1">
-        <v>-0.17394092679023743</v>
+        <v>-0.14167046546936035</v>
       </c>
     </row>
     <row r="224">
@@ -2531,7 +2529,7 @@
         <v>0.31227210164070129</v>
       </c>
       <c r="C224" s="1">
-        <v>-0.30167907476425171</v>
+        <v>-0.27671587467193604</v>
       </c>
     </row>
     <row r="225">
@@ -2542,7 +2540,7 @@
         <v>0.3199465274810791</v>
       </c>
       <c r="C225" s="1">
-        <v>0.11659648269414902</v>
+        <v>0.078771926462650299</v>
       </c>
     </row>
     <row r="226">
@@ -2553,7 +2551,7 @@
         <v>-0.11365824192762375</v>
       </c>
       <c r="C226" s="1">
-        <v>-0.47630155086517334</v>
+        <v>-0.3651917576789856</v>
       </c>
     </row>
     <row r="227">
@@ -2564,7 +2562,7 @@
         <v>0.4262920618057251</v>
       </c>
       <c r="C227" s="1">
-        <v>-0.22391168773174286</v>
+        <v>-0.17699132859706879</v>
       </c>
     </row>
     <row r="228">
@@ -2575,7 +2573,7 @@
         <v>-0.05774461105465889</v>
       </c>
       <c r="C228" s="1">
-        <v>-0.11401630192995071</v>
+        <v>-0.060009844601154327</v>
       </c>
     </row>
     <row r="229">
@@ -2586,7 +2584,7 @@
         <v>0.35009601712226868</v>
       </c>
       <c r="C229" s="1">
-        <v>-0.10875273495912552</v>
+        <v>-0.10306559503078461</v>
       </c>
     </row>
     <row r="230">
@@ -2597,7 +2595,7 @@
         <v>-0.12462169677019119</v>
       </c>
       <c r="C230" s="1">
-        <v>-0.15219397842884064</v>
+        <v>-0.11363517493009567</v>
       </c>
     </row>
     <row r="231">
@@ -2605,10 +2603,10 @@
         <v>199402</v>
       </c>
       <c r="B231" s="1">
-        <v>-0.22603368759155273</v>
+        <v>-0.22603368759155274</v>
       </c>
       <c r="C231" s="1">
-        <v>-0.058991298079490662</v>
+        <v>-0.036489870399236679</v>
       </c>
     </row>
     <row r="232">
@@ -2619,7 +2617,7 @@
         <v>0.038733825087547302</v>
       </c>
       <c r="C232" s="1">
-        <v>-0.26590320467948914</v>
+        <v>-0.22160437703132629</v>
       </c>
     </row>
     <row r="233">
@@ -2630,7 +2628,7 @@
         <v>0.23881691694259644</v>
       </c>
       <c r="C233" s="1">
-        <v>-0.10609856992959976</v>
+        <v>-0.072917692363262177</v>
       </c>
     </row>
     <row r="234">
@@ -2641,7 +2639,7 @@
         <v>-0.37513670325279236</v>
       </c>
       <c r="C234" s="1">
-        <v>-0.079999871551990509</v>
+        <v>-0.050805382430553436</v>
       </c>
     </row>
     <row r="235">
@@ -2652,7 +2650,7 @@
         <v>-0.20684763789176941</v>
       </c>
       <c r="C235" s="1">
-        <v>-0.076034024357795715</v>
+        <v>-0.03117496520280838</v>
       </c>
     </row>
     <row r="236">
@@ -2663,7 +2661,7 @@
         <v>0.19605943560600281</v>
       </c>
       <c r="C236" s="1">
-        <v>-0.33386555314064026</v>
+        <v>-0.2856408953666687</v>
       </c>
     </row>
     <row r="237">
@@ -2674,7 +2672,7 @@
         <v>0.11767071485519409</v>
       </c>
       <c r="C237" s="1">
-        <v>0.010710506699979305</v>
+        <v>-0.019386505708098412</v>
       </c>
     </row>
     <row r="238">
@@ -2685,7 +2683,7 @@
         <v>-0.46503707766532898</v>
       </c>
       <c r="C238" s="1">
-        <v>0.069238834083080292</v>
+        <v>0.10083574801683426</v>
       </c>
     </row>
     <row r="239">
@@ -2696,7 +2694,7 @@
         <v>0.092454761266708374</v>
       </c>
       <c r="C239" s="1">
-        <v>0.21099916100502014</v>
+        <v>0.13763967156410217</v>
       </c>
     </row>
     <row r="240">
@@ -2707,7 +2705,7 @@
         <v>-0.1322961151599884</v>
       </c>
       <c r="C240" s="1">
-        <v>0.04910866916179657</v>
+        <v>0.072077050805091858</v>
       </c>
     </row>
     <row r="241">
@@ -2718,7 +2716,7 @@
         <v>0.083683997392654419</v>
       </c>
       <c r="C241" s="1">
-        <v>0.14885888993740082</v>
+        <v>0.099206097424030304</v>
       </c>
     </row>
     <row r="242">
@@ -2729,7 +2727,7 @@
         <v>-0.24741242825984955</v>
       </c>
       <c r="C242" s="1">
-        <v>-0.38894519209861755</v>
+        <v>-0.24042540788650513</v>
       </c>
     </row>
     <row r="243">
@@ -2740,7 +2738,7 @@
         <v>0.18619233369827271</v>
       </c>
       <c r="C243" s="1">
-        <v>0.073634698987007141</v>
+        <v>0.026653837412595749</v>
       </c>
     </row>
     <row r="244">
@@ -2751,7 +2749,7 @@
         <v>-0.49573478102684021</v>
       </c>
       <c r="C244" s="1">
-        <v>-0.4647713303565979</v>
+        <v>-0.34082823991775513</v>
       </c>
     </row>
     <row r="245">
@@ -2762,7 +2760,7 @@
         <v>0.22785347700119019</v>
       </c>
       <c r="C245" s="1">
-        <v>-0.059098426252603531</v>
+        <v>-0.087691672146320343</v>
       </c>
     </row>
     <row r="246">
@@ -2770,10 +2768,10 @@
         <v>199505</v>
       </c>
       <c r="B246" s="1">
-        <v>0.13740494847297668</v>
+        <v>0.13740494847297669</v>
       </c>
       <c r="C246" s="1">
-        <v>0.055657025426626205</v>
+        <v>0.043770685791969299</v>
       </c>
     </row>
     <row r="247">
@@ -2784,7 +2782,7 @@
         <v>-0.0023791471030563116</v>
       </c>
       <c r="C247" s="1">
-        <v>-0.22636738419532776</v>
+        <v>-0.1608719527721405</v>
       </c>
     </row>
     <row r="248">
@@ -2795,7 +2793,7 @@
         <v>0.25635844469070435</v>
       </c>
       <c r="C248" s="1">
-        <v>-0.23111194372177124</v>
+        <v>-0.22663465142250061</v>
       </c>
     </row>
     <row r="249">
@@ -2806,7 +2804,7 @@
         <v>0.00090988969895988703</v>
       </c>
       <c r="C249" s="1">
-        <v>-0.13314239680767059</v>
+        <v>-0.099278204143047333</v>
       </c>
     </row>
     <row r="250">
@@ -2817,7 +2815,7 @@
         <v>-0.1460004448890686</v>
       </c>
       <c r="C250" s="1">
-        <v>0.19571408629417419</v>
+        <v>0.192291259765625</v>
       </c>
     </row>
     <row r="251">
@@ -2828,7 +2826,7 @@
         <v>-0.14654861390590668</v>
       </c>
       <c r="C251" s="1">
-        <v>-0.53891617059707642</v>
+        <v>-0.46204179525375366</v>
       </c>
     </row>
     <row r="252">
@@ -2839,7 +2837,7 @@
         <v>0.082587644457817078</v>
       </c>
       <c r="C252" s="1">
-        <v>-0.028421096503734589</v>
+        <v>-0.0026050542946904898</v>
       </c>
     </row>
     <row r="253">
@@ -2850,7 +2848,7 @@
         <v>0.08094312995672226</v>
       </c>
       <c r="C253" s="1">
-        <v>-0.051466621458530426</v>
+        <v>-0.068143360316753387</v>
       </c>
     </row>
     <row r="254">
@@ -2861,7 +2859,7 @@
         <v>0.38463091850280762</v>
       </c>
       <c r="C254" s="1">
-        <v>0.077311128377914429</v>
+        <v>0.021177135407924652</v>
       </c>
     </row>
     <row r="255">
@@ -2872,7 +2870,7 @@
         <v>-0.04732932522892952</v>
       </c>
       <c r="C255" s="1">
-        <v>-0.2828725278377533</v>
+        <v>-0.22459027171134949</v>
       </c>
     </row>
     <row r="256">
@@ -2883,7 +2881,7 @@
         <v>-0.031432311981916428</v>
       </c>
       <c r="C256" s="1">
-        <v>-0.0275137759745121</v>
+        <v>-0.017284838482737541</v>
       </c>
     </row>
     <row r="257">
@@ -2894,7 +2892,7 @@
         <v>-0.052811052650213242</v>
       </c>
       <c r="C257" s="1">
-        <v>-0.11519983410835266</v>
+        <v>-0.08519415557384491</v>
       </c>
     </row>
     <row r="258">
@@ -2905,7 +2903,7 @@
         <v>0.033800262957811356</v>
       </c>
       <c r="C258" s="1">
-        <v>-0.032725289463996887</v>
+        <v>-0.00017528994067106396</v>
       </c>
     </row>
     <row r="259">
@@ -2916,7 +2914,7 @@
         <v>0.074913226068019867</v>
       </c>
       <c r="C259" s="1">
-        <v>-0.055994328111410141</v>
+        <v>-0.025341110303997994</v>
       </c>
     </row>
     <row r="260">
@@ -2927,7 +2925,7 @@
         <v>-0.22822637856006622</v>
       </c>
       <c r="C260" s="1">
-        <v>-0.28760239481925964</v>
+        <v>-0.25076073408126831</v>
       </c>
     </row>
     <row r="261">
@@ -2938,7 +2936,7 @@
         <v>0.10451456159353256</v>
       </c>
       <c r="C261" s="1">
-        <v>-0.16517652571201324</v>
+        <v>-0.11668457835912704</v>
       </c>
     </row>
     <row r="262">
@@ -2949,7 +2947,7 @@
         <v>0.17577706277370453</v>
       </c>
       <c r="C262" s="1">
-        <v>-0.063210062682628632</v>
+        <v>-0.03221617266535759</v>
       </c>
     </row>
     <row r="263">
@@ -2960,7 +2958,7 @@
         <v>-0.019920680671930313</v>
       </c>
       <c r="C263" s="1">
-        <v>-0.27258503437042236</v>
+        <v>-0.2151152491569519</v>
       </c>
     </row>
     <row r="264">
@@ -2971,7 +2969,7 @@
         <v>0.26458105444908142</v>
       </c>
       <c r="C264" s="1">
-        <v>-0.057249832898378372</v>
+        <v>-0.086101308465003967</v>
       </c>
     </row>
     <row r="265">
@@ -2982,7 +2980,7 @@
         <v>0.07107602059841156</v>
       </c>
       <c r="C265" s="1">
-        <v>0.0093081481754779816</v>
+        <v>-0.016797244548797607</v>
       </c>
     </row>
     <row r="266">
@@ -2993,7 +2991,7 @@
         <v>0.22675712406635284</v>
       </c>
       <c r="C266" s="1">
-        <v>-0.18650315701961517</v>
+        <v>-0.21849992871284485</v>
       </c>
     </row>
     <row r="267">
@@ -3001,10 +2999,10 @@
         <v>199702</v>
       </c>
       <c r="B267" s="1">
-        <v>0.3435179591178894</v>
+        <v>0.34351795911788941</v>
       </c>
       <c r="C267" s="1">
-        <v>0.24745637178421021</v>
+        <v>0.21692146360874176</v>
       </c>
     </row>
     <row r="268">
@@ -3015,7 +3013,7 @@
         <v>0.27335181832313538</v>
       </c>
       <c r="C268" s="1">
-        <v>-0.059926409274339676</v>
+        <v>0.0084889642894268036</v>
       </c>
     </row>
     <row r="269">
@@ -3026,7 +3024,7 @@
         <v>-0.028143273666501045</v>
       </c>
       <c r="C269" s="1">
-        <v>-0.10396452993154526</v>
+        <v>-0.10699779540300369</v>
       </c>
     </row>
     <row r="270">
@@ -3034,10 +3032,10 @@
         <v>199705</v>
       </c>
       <c r="B270" s="1">
-        <v>0.093551106750965118</v>
+        <v>0.093551106750965119</v>
       </c>
       <c r="C270" s="1">
-        <v>-0.25087130069732666</v>
+        <v>-0.22782009840011597</v>
       </c>
     </row>
     <row r="271">
@@ -3048,7 +3046,7 @@
         <v>0.29911595582962036</v>
       </c>
       <c r="C271" s="1">
-        <v>0.35558104515075684</v>
+        <v>0.30223369598388672</v>
       </c>
     </row>
     <row r="272">
@@ -3059,7 +3057,7 @@
         <v>0.72175717353820801</v>
       </c>
       <c r="C272" s="1">
-        <v>0.13654723763465881</v>
+        <v>0.064897142350673676</v>
       </c>
     </row>
     <row r="273">
@@ -3070,7 +3068,7 @@
         <v>-0.65689754486083984</v>
       </c>
       <c r="C273" s="1">
-        <v>-0.19732969999313354</v>
+        <v>-0.14271977543830872</v>
       </c>
     </row>
     <row r="274">
@@ -3081,7 +3079,7 @@
         <v>0.24046143889427185</v>
       </c>
       <c r="C274" s="1">
-        <v>-0.083084061741828918</v>
+        <v>-0.10937943309545517</v>
       </c>
     </row>
     <row r="275">
@@ -3092,7 +3090,7 @@
         <v>-0.54726302623748779</v>
       </c>
       <c r="C275" s="1">
-        <v>0.022192744538187981</v>
+        <v>0.066027261316776276</v>
       </c>
     </row>
     <row r="276">
@@ -3103,7 +3101,7 @@
         <v>0.23936508595943451</v>
       </c>
       <c r="C276" s="1">
-        <v>-0.11726109683513641</v>
+        <v>-0.083723515272140503</v>
       </c>
     </row>
     <row r="277">
@@ -3114,7 +3112,7 @@
         <v>0.25197309255599976</v>
       </c>
       <c r="C277" s="1">
-        <v>0.10161136835813522</v>
+        <v>0.099491983652114868</v>
       </c>
     </row>
     <row r="278">
@@ -3125,7 +3123,7 @@
         <v>0.19112588465213776</v>
       </c>
       <c r="C278" s="1">
-        <v>0.11355390399694443</v>
+        <v>0.21826119720935822</v>
       </c>
     </row>
     <row r="279">
@@ -3136,7 +3134,7 @@
         <v>0.28760433197021484</v>
       </c>
       <c r="C279" s="1">
-        <v>-0.15492850542068481</v>
+        <v>-0.11514290422201157</v>
       </c>
     </row>
     <row r="280">
@@ -3147,7 +3145,7 @@
         <v>0.41478043794631958</v>
       </c>
       <c r="C280" s="1">
-        <v>0.24248236417770386</v>
+        <v>0.15243473649024963</v>
       </c>
     </row>
     <row r="281">
@@ -3158,7 +3156,7 @@
         <v>0.0041989265009760857</v>
       </c>
       <c r="C281" s="1">
-        <v>-0.21249905228614807</v>
+        <v>-0.14924278855323792</v>
       </c>
     </row>
     <row r="282">
@@ -3169,7 +3167,7 @@
         <v>0.32159101963043213</v>
       </c>
       <c r="C282" s="1">
-        <v>-0.064237885177135468</v>
+        <v>-0.11035870015621185</v>
       </c>
     </row>
     <row r="283">
@@ -3180,7 +3178,7 @@
         <v>0.22291991114616394</v>
       </c>
       <c r="C283" s="1">
-        <v>0.060937356203794479</v>
+        <v>0.014093350619077683</v>
       </c>
     </row>
     <row r="284">
@@ -3191,7 +3189,7 @@
         <v>-0.043492116034030914</v>
       </c>
       <c r="C284" s="1">
-        <v>0.15246392786502838</v>
+        <v>0.15176497399806976</v>
       </c>
     </row>
     <row r="285">
@@ -3202,7 +3200,7 @@
         <v>-0.94797742366790771</v>
       </c>
       <c r="C285" s="1">
-        <v>-0.022921280935406685</v>
+        <v>-0.00085406727157533169</v>
       </c>
     </row>
     <row r="286">
@@ -3213,7 +3211,7 @@
         <v>-0.38335931301116943</v>
       </c>
       <c r="C286" s="1">
-        <v>-0.14608727395534515</v>
+        <v>-0.13478502631187439</v>
       </c>
     </row>
     <row r="287">
@@ -3224,7 +3222,7 @@
         <v>0.11767071485519409</v>
       </c>
       <c r="C287" s="1">
-        <v>-0.10604561120271683</v>
+        <v>-0.073573336005210877</v>
       </c>
     </row>
     <row r="288">
@@ -3235,7 +3233,7 @@
         <v>0.32488009333610535</v>
       </c>
       <c r="C288" s="1">
-        <v>-0.039406731724739075</v>
+        <v>-0.06922457367181778</v>
       </c>
     </row>
     <row r="289">
@@ -3243,10 +3241,10 @@
         <v>199812</v>
       </c>
       <c r="B289" s="1">
-        <v>0.0069397916086018085</v>
+        <v>0.0069397916086018086</v>
       </c>
       <c r="C289" s="1">
-        <v>0.13340446352958679</v>
+        <v>0.080828547477722168</v>
       </c>
     </row>
     <row r="290">
@@ -3257,7 +3255,7 @@
         <v>0.18728868663311005</v>
       </c>
       <c r="C290" s="1">
-        <v>0.22835506498813629</v>
+        <v>0.35137626528739929</v>
       </c>
     </row>
     <row r="291">
@@ -3268,7 +3266,7 @@
         <v>-0.22493734955787659</v>
       </c>
       <c r="C291" s="1">
-        <v>0.14608584344387054</v>
+        <v>0.1088607981801033</v>
       </c>
     </row>
     <row r="292">
@@ -3279,7 +3277,7 @@
         <v>-0.11804362386465073</v>
       </c>
       <c r="C292" s="1">
-        <v>0.14539428055286407</v>
+        <v>0.11114038527011871</v>
       </c>
     </row>
     <row r="293">
@@ -3290,7 +3288,7 @@
         <v>0.37860098481178284</v>
       </c>
       <c r="C293" s="1">
-        <v>0.15172898769378662</v>
+        <v>0.048091556876897812</v>
       </c>
     </row>
     <row r="294">
@@ -3301,7 +3299,7 @@
         <v>-0.28468817472457886</v>
       </c>
       <c r="C294" s="1">
-        <v>0.17642918229103088</v>
+        <v>0.22492150962352753</v>
       </c>
     </row>
     <row r="295">
@@ -3312,7 +3310,7 @@
         <v>0.28870067000389099</v>
       </c>
       <c r="C295" s="1">
-        <v>0.092810727655887604</v>
+        <v>0.039879541844129562</v>
       </c>
     </row>
     <row r="296">
@@ -3323,7 +3321,7 @@
         <v>-0.26550212502479553</v>
       </c>
       <c r="C296" s="1">
-        <v>0.16663661599159241</v>
+        <v>0.15206418931484223</v>
       </c>
     </row>
     <row r="297">
@@ -3334,7 +3332,7 @@
         <v>0.13301955163478851</v>
       </c>
       <c r="C297" s="1">
-        <v>-0.038238715380430222</v>
+        <v>-0.067007578909397125</v>
       </c>
     </row>
     <row r="298">
@@ -3345,7 +3343,7 @@
         <v>-0.14983765780925751</v>
       </c>
       <c r="C298" s="1">
-        <v>0.061449345201253891</v>
+        <v>0.12503357231616974</v>
       </c>
     </row>
     <row r="299">
@@ -3356,7 +3354,7 @@
         <v>0.28321895003318787</v>
       </c>
       <c r="C299" s="1">
-        <v>-0.10270905494689941</v>
+        <v>-0.095790229737758636</v>
       </c>
     </row>
     <row r="300">
@@ -3367,7 +3365,7 @@
         <v>0.28157439827919006</v>
       </c>
       <c r="C300" s="1">
-        <v>0.18769198656082153</v>
+        <v>0.14881710708141327</v>
       </c>
     </row>
     <row r="301">
@@ -3378,7 +3376,7 @@
         <v>0.87305301427841187</v>
       </c>
       <c r="C301" s="1">
-        <v>0.067067712545394897</v>
+        <v>0.041020423173904419</v>
       </c>
     </row>
     <row r="302">
@@ -3389,7 +3387,7 @@
         <v>-0.1185918003320694</v>
       </c>
       <c r="C302" s="1">
-        <v>0.097733236849308014</v>
+        <v>0.11019092798233032</v>
       </c>
     </row>
     <row r="303">
@@ -3400,7 +3398,7 @@
         <v>0.58416587114334106</v>
       </c>
       <c r="C303" s="1">
-        <v>0.35566985607147217</v>
+        <v>0.29110285639762879</v>
       </c>
     </row>
     <row r="304">
@@ -3411,7 +3409,7 @@
         <v>-0.045136634260416031</v>
       </c>
       <c r="C304" s="1">
-        <v>0.0092329420149326324</v>
+        <v>0.017336564138531685</v>
       </c>
     </row>
     <row r="305">
@@ -3422,7 +3420,7 @@
         <v>-0.24686427414417267</v>
       </c>
       <c r="C305" s="1">
-        <v>0.32734483480453491</v>
+        <v>0.34783515334129333</v>
       </c>
     </row>
     <row r="306">
@@ -3433,7 +3431,7 @@
         <v>-0.26495397090911865</v>
       </c>
       <c r="C306" s="1">
-        <v>0.48357021808624268</v>
+        <v>0.38704341650009155</v>
       </c>
     </row>
     <row r="307">
@@ -3444,7 +3442,7 @@
         <v>-0.21287752687931061</v>
       </c>
       <c r="C307" s="1">
-        <v>-0.57807427644729614</v>
+        <v>-0.48379746079444885</v>
       </c>
     </row>
     <row r="308">
@@ -3455,7 +3453,7 @@
         <v>0.15275378525257111</v>
       </c>
       <c r="C308" s="1">
-        <v>0.43514490127563477</v>
+        <v>0.3222673237323761</v>
       </c>
     </row>
     <row r="309">
@@ -3466,7 +3464,7 @@
         <v>-0.039106730371713638</v>
       </c>
       <c r="C309" s="1">
-        <v>0.25851744413375854</v>
+        <v>0.19252777099609375</v>
       </c>
     </row>
     <row r="310">
@@ -3477,7 +3475,7 @@
         <v>-0.25508686900138855</v>
       </c>
       <c r="C310" s="1">
-        <v>0.14923764765262604</v>
+        <v>0.10288271307945251</v>
       </c>
     </row>
     <row r="311">
@@ -3488,7 +3486,7 @@
         <v>0.19770394265651703</v>
       </c>
       <c r="C311" s="1">
-        <v>0.099898852407932281</v>
+        <v>0.079295307397842407</v>
       </c>
     </row>
     <row r="312">
@@ -3499,7 +3497,7 @@
         <v>-0.56809359788894653</v>
       </c>
       <c r="C312" s="1">
-        <v>0.0079040974378585815</v>
+        <v>0.058458331972360611</v>
       </c>
     </row>
     <row r="313">
@@ -3510,7 +3508,7 @@
         <v>0.015710558742284775</v>
       </c>
       <c r="C313" s="1">
-        <v>-0.14706520736217499</v>
+        <v>-0.12397634983062744</v>
       </c>
     </row>
     <row r="314">
@@ -3521,7 +3519,7 @@
         <v>0.20757107436656952</v>
       </c>
       <c r="C314" s="1">
-        <v>-0.35280364751815796</v>
+        <v>-0.21609893441200256</v>
       </c>
     </row>
     <row r="315">
@@ -3532,7 +3530,7 @@
         <v>-0.45626631379127502</v>
       </c>
       <c r="C315" s="1">
-        <v>0.17770321667194366</v>
+        <v>0.11263323575258255</v>
       </c>
     </row>
     <row r="316">
@@ -3543,7 +3541,7 @@
         <v>-0.38774469494819641</v>
       </c>
       <c r="C316" s="1">
-        <v>0.13710200786590576</v>
+        <v>0.10575223714113235</v>
       </c>
     </row>
     <row r="317">
@@ -3554,7 +3552,7 @@
         <v>0.30733853578567505</v>
       </c>
       <c r="C317" s="1">
-        <v>-0.16554719209671021</v>
+        <v>-0.16196781396865845</v>
       </c>
     </row>
     <row r="318">
@@ -3565,7 +3563,7 @@
         <v>-0.17889082431793213</v>
       </c>
       <c r="C318" s="1">
-        <v>-0.005828456487506628</v>
+        <v>-0.047748912125825882</v>
       </c>
     </row>
     <row r="319">
@@ -3576,7 +3574,7 @@
         <v>-0.12352535873651505</v>
       </c>
       <c r="C319" s="1">
-        <v>0.03792523592710495</v>
+        <v>0.066473096609115601</v>
       </c>
     </row>
     <row r="320">
@@ -3587,7 +3585,7 @@
         <v>-0.19588418304920197</v>
       </c>
       <c r="C320" s="1">
-        <v>-0.50685775279998779</v>
+        <v>-0.33727902173995972</v>
       </c>
     </row>
     <row r="321">
@@ -3598,7 +3596,7 @@
         <v>-0.57631611824035645</v>
       </c>
       <c r="C321" s="1">
-        <v>0.024729505181312561</v>
+        <v>0.066175773739814758</v>
       </c>
     </row>
     <row r="322">
@@ -3609,7 +3607,7 @@
         <v>-0.92933946847915649</v>
       </c>
       <c r="C322" s="1">
-        <v>-0.32136890292167664</v>
+        <v>-0.19262228906154633</v>
       </c>
     </row>
     <row r="323">
@@ -3620,7 +3618,7 @@
         <v>0.32652458548545837</v>
       </c>
       <c r="C323" s="1">
-        <v>-0.32563367486000061</v>
+        <v>-0.30445772409439087</v>
       </c>
     </row>
     <row r="324">
@@ -3631,7 +3629,7 @@
         <v>0.46466416120529175</v>
       </c>
       <c r="C324" s="1">
-        <v>-0.13362894952297211</v>
+        <v>-0.061100691556930542</v>
       </c>
     </row>
     <row r="325">
@@ -3642,7 +3640,7 @@
         <v>0.10287004709243774</v>
       </c>
       <c r="C325" s="1">
-        <v>-0.15287628769874573</v>
+        <v>-0.12378554046154022</v>
       </c>
     </row>
     <row r="326">
@@ -3653,7 +3651,7 @@
         <v>-0.056648265570402145</v>
       </c>
       <c r="C326" s="1">
-        <v>-0.044523525983095169</v>
+        <v>-0.025945037603378296</v>
       </c>
     </row>
     <row r="327">
@@ -3664,7 +3662,7 @@
         <v>-0.12845891714096069</v>
       </c>
       <c r="C327" s="1">
-        <v>-0.1140558049082756</v>
+        <v>-0.077996477484703064</v>
       </c>
     </row>
     <row r="328">
@@ -3675,7 +3673,7 @@
         <v>0.31501296162605286</v>
       </c>
       <c r="C328" s="1">
-        <v>-0.095573559403419495</v>
+        <v>-0.087898343801498413</v>
       </c>
     </row>
     <row r="329">
@@ -3686,7 +3684,7 @@
         <v>-0.39048555493354797</v>
       </c>
       <c r="C329" s="1">
-        <v>-0.2113080769777298</v>
+        <v>-0.12847459316253662</v>
       </c>
     </row>
     <row r="330">
@@ -3697,7 +3695,7 @@
         <v>-0.31812673807144165</v>
       </c>
       <c r="C330" s="1">
-        <v>-0.4403921365737915</v>
+        <v>-0.28175655007362366</v>
       </c>
     </row>
     <row r="331">
@@ -3708,7 +3706,7 @@
         <v>-0.55110019445419312</v>
       </c>
       <c r="C331" s="1">
-        <v>-0.066782936453819275</v>
+        <v>-0.059760924428701401</v>
       </c>
     </row>
     <row r="332">
@@ -3719,7 +3717,7 @@
         <v>-0.8284757137298584</v>
       </c>
       <c r="C332" s="1">
-        <v>-0.45600661635398865</v>
+        <v>-0.33079901337623596</v>
       </c>
     </row>
     <row r="333">
@@ -3730,7 +3728,7 @@
         <v>-0.038010384887456894</v>
       </c>
       <c r="C333" s="1">
-        <v>0.16431887447834015</v>
+        <v>0.11261368542909622</v>
       </c>
     </row>
     <row r="334">
@@ -3741,7 +3739,7 @@
         <v>-1.3574625253677368</v>
       </c>
       <c r="C334" s="1">
-        <v>-0.21041309833526611</v>
+        <v>-0.13188230991363525</v>
       </c>
     </row>
     <row r="335">
@@ -3752,7 +3750,7 @@
         <v>0.7409433126449585</v>
       </c>
       <c r="C335" s="1">
-        <v>-0.37793320417404175</v>
+        <v>-0.31603088974952698</v>
       </c>
     </row>
     <row r="336">
@@ -3763,7 +3761,7 @@
         <v>0.1823551207780838</v>
       </c>
       <c r="C336" s="1">
-        <v>-0.19888338446617126</v>
+        <v>-0.086656756699085236</v>
       </c>
     </row>
     <row r="337">
@@ -3774,7 +3772,7 @@
         <v>-0.66183114051818848</v>
       </c>
       <c r="C337" s="1">
-        <v>-0.38278356194496155</v>
+        <v>-0.2761208713054657</v>
       </c>
     </row>
     <row r="338">
@@ -3785,7 +3783,7 @@
         <v>-0.28742906451225281</v>
       </c>
       <c r="C338" s="1">
-        <v>-0.41184625029563904</v>
+        <v>-0.36089488863945007</v>
       </c>
     </row>
     <row r="339">
@@ -3796,7 +3794,7 @@
         <v>-0.42611679434776306</v>
       </c>
       <c r="C339" s="1">
-        <v>-0.18942040205001831</v>
+        <v>-0.10924523323774338</v>
       </c>
     </row>
     <row r="340">
@@ -3807,7 +3805,7 @@
         <v>-0.27372473478317261</v>
       </c>
       <c r="C340" s="1">
-        <v>-0.17745594680309296</v>
+        <v>-0.14454679191112518</v>
       </c>
     </row>
     <row r="341">
@@ -3818,7 +3816,7 @@
         <v>1.0122888088226318</v>
       </c>
       <c r="C341" s="1">
-        <v>-0.38633984327316284</v>
+        <v>-0.25704744458198547</v>
       </c>
     </row>
     <row r="342">
@@ -3829,7 +3827,7 @@
         <v>0.047504588961601257</v>
       </c>
       <c r="C342" s="1">
-        <v>-0.45746994018554688</v>
+        <v>-0.31805795431137085</v>
       </c>
     </row>
     <row r="343">
@@ -3840,7 +3838,7 @@
         <v>0.34899967908859253</v>
       </c>
       <c r="C343" s="1">
-        <v>-0.34218427538871765</v>
+        <v>-0.28952440619468689</v>
       </c>
     </row>
     <row r="344">
@@ -3851,7 +3849,7 @@
         <v>0.34954783320426941</v>
       </c>
       <c r="C344" s="1">
-        <v>0.28993514180183411</v>
+        <v>0.1978127509355545</v>
       </c>
     </row>
     <row r="345">
@@ -3862,7 +3860,7 @@
         <v>0.020644115284085274</v>
       </c>
       <c r="C345" s="1">
-        <v>-0.18835031986236572</v>
+        <v>-0.14470948278903961</v>
       </c>
     </row>
     <row r="346">
@@ -3873,7 +3871,7 @@
         <v>-0.3603360652923584</v>
       </c>
       <c r="C346" s="1">
-        <v>-0.064423896372318268</v>
+        <v>-0.062642447650432587</v>
       </c>
     </row>
     <row r="347">
@@ -3884,7 +3882,7 @@
         <v>0.60390007495880127</v>
       </c>
       <c r="C347" s="1">
-        <v>-0.069630637764930725</v>
+        <v>-0.10476179420948029</v>
       </c>
     </row>
     <row r="348">
@@ -3895,7 +3893,7 @@
         <v>0.045860070735216141</v>
       </c>
       <c r="C348" s="1">
-        <v>-0.028152061626315117</v>
+        <v>0.060592804104089737</v>
       </c>
     </row>
     <row r="349">
@@ -3906,7 +3904,7 @@
         <v>0.21743817627429962</v>
       </c>
       <c r="C349" s="1">
-        <v>-0.21488741040229797</v>
+        <v>-0.21859017014503479</v>
       </c>
     </row>
     <row r="350">
@@ -3917,7 +3915,7 @@
         <v>0.12205609679222107</v>
       </c>
       <c r="C350" s="1">
-        <v>-0.21509496867656708</v>
+        <v>-0.25741466879844666</v>
       </c>
     </row>
     <row r="351">
@@ -3928,7 +3926,7 @@
         <v>-0.068708069622516632</v>
       </c>
       <c r="C351" s="1">
-        <v>-0.31368741393089294</v>
+        <v>-0.27640452980995178</v>
       </c>
     </row>
     <row r="352">
@@ -3939,7 +3937,7 @@
         <v>-0.24796061217784882</v>
       </c>
       <c r="C352" s="1">
-        <v>-0.20348964631557465</v>
+        <v>-0.14103817939758301</v>
       </c>
     </row>
     <row r="353">
@@ -3950,7 +3948,7 @@
         <v>0.073268711566925049</v>
       </c>
       <c r="C353" s="1">
-        <v>0.16933867335319519</v>
+        <v>0.12513560056686401</v>
       </c>
     </row>
     <row r="354">
@@ -3961,7 +3959,7 @@
         <v>-0.15422303974628448</v>
       </c>
       <c r="C354" s="1">
-        <v>0.0051246252842247486</v>
+        <v>0.01831343024969101</v>
       </c>
     </row>
     <row r="355">
@@ -3972,7 +3970,7 @@
         <v>0.12479697912931442</v>
       </c>
       <c r="C355" s="1">
-        <v>-0.1474945992231369</v>
+        <v>-0.15355932712554932</v>
       </c>
     </row>
     <row r="356">
@@ -3983,7 +3981,7 @@
         <v>-0.23590080440044403</v>
       </c>
       <c r="C356" s="1">
-        <v>0.030743274837732315</v>
+        <v>0.061383627355098724</v>
       </c>
     </row>
     <row r="357">
@@ -3994,7 +3992,7 @@
         <v>-0.21287752687931061</v>
       </c>
       <c r="C357" s="1">
-        <v>-0.24127954244613647</v>
+        <v>-0.19711273908615112</v>
       </c>
     </row>
     <row r="358">
@@ -4005,7 +4003,7 @@
         <v>0.10067736357450485</v>
       </c>
       <c r="C358" s="1">
-        <v>-0.046338941901922226</v>
+        <v>-0.068775869905948639</v>
       </c>
     </row>
     <row r="359">
@@ -4016,7 +4014,7 @@
         <v>0.035444781184196472</v>
       </c>
       <c r="C359" s="1">
-        <v>-0.17448438704013824</v>
+        <v>-0.13915398716926575</v>
       </c>
     </row>
     <row r="360">
@@ -4027,7 +4025,7 @@
         <v>0.17961426079273224</v>
       </c>
       <c r="C360" s="1">
-        <v>-0.58228999376296997</v>
+        <v>-0.40305164456367493</v>
       </c>
     </row>
     <row r="361">
@@ -4038,7 +4036,7 @@
         <v>0.12644147872924805</v>
       </c>
       <c r="C361" s="1">
-        <v>-0.3508429229259491</v>
+        <v>-0.30814480781555176</v>
       </c>
     </row>
     <row r="362">
@@ -4049,7 +4047,7 @@
         <v>-0.022113371640443802</v>
       </c>
       <c r="C362" s="1">
-        <v>0.25355479121208191</v>
+        <v>0.27681690454483032</v>
       </c>
     </row>
     <row r="363">
@@ -4060,7 +4058,7 @@
         <v>0.083135828375816345</v>
       </c>
       <c r="C363" s="1">
-        <v>-0.38249579071998596</v>
+        <v>-0.28638631105422974</v>
       </c>
     </row>
     <row r="364">
@@ -4071,7 +4069,7 @@
         <v>-0.045684807002544403</v>
       </c>
       <c r="C364" s="1">
-        <v>-0.025278285145759583</v>
+        <v>-0.032210029661655426</v>
       </c>
     </row>
     <row r="365">
@@ -4082,7 +4080,7 @@
         <v>-0.30003702640533447</v>
       </c>
       <c r="C365" s="1">
-        <v>-0.10787057131528854</v>
+        <v>-0.094895429909229279</v>
       </c>
     </row>
     <row r="366">
@@ -4093,7 +4091,7 @@
         <v>0.28212261199951172</v>
       </c>
       <c r="C366" s="1">
-        <v>-0.036948058754205704</v>
+        <v>-0.066000059247016907</v>
       </c>
     </row>
     <row r="367">
@@ -4104,7 +4102,7 @@
         <v>0.13630859553813934</v>
       </c>
       <c r="C367" s="1">
-        <v>0.32176885008811951</v>
+        <v>0.26986327767372131</v>
       </c>
     </row>
     <row r="368">
@@ -4115,7 +4113,7 @@
         <v>0.294730544090271</v>
       </c>
       <c r="C368" s="1">
-        <v>0.059513825923204422</v>
+        <v>0.043501954525709152</v>
       </c>
     </row>
     <row r="369">
@@ -4126,7 +4124,7 @@
         <v>-0.092279501259326935</v>
       </c>
       <c r="C369" s="1">
-        <v>-0.43945249915122986</v>
+        <v>-0.36798527836799622</v>
       </c>
     </row>
     <row r="370">
@@ -4137,7 +4135,7 @@
         <v>0.19002953171730042</v>
       </c>
       <c r="C370" s="1">
-        <v>0.24819928407669067</v>
+        <v>0.2009611576795578</v>
       </c>
     </row>
     <row r="371">
@@ -4148,7 +4146,7 @@
         <v>-0.19423966109752655</v>
       </c>
       <c r="C371" s="1">
-        <v>0.31297558546066284</v>
+        <v>0.27421164512634277</v>
       </c>
     </row>
     <row r="372">
@@ -4159,7 +4157,7 @@
         <v>0.21140827238559723</v>
       </c>
       <c r="C372" s="1">
-        <v>-0.0045943879522383213</v>
+        <v>0.073470890522003174</v>
       </c>
     </row>
     <row r="373">
@@ -4170,7 +4168,7 @@
         <v>0.18180693686008453</v>
       </c>
       <c r="C373" s="1">
-        <v>0.068449035286903381</v>
+        <v>0.072223357856273651</v>
       </c>
     </row>
     <row r="374">
@@ -4181,7 +4179,7 @@
         <v>0.23662422597408295</v>
       </c>
       <c r="C374" s="1">
-        <v>-0.008238120935857296</v>
+        <v>-0.013913311995565891</v>
       </c>
     </row>
     <row r="375">
@@ -4192,7 +4190,7 @@
         <v>0.12644147872924805</v>
       </c>
       <c r="C375" s="1">
-        <v>0.10167082399129868</v>
+        <v>0.086646676063537598</v>
       </c>
     </row>
     <row r="376">
@@ -4203,7 +4201,7 @@
         <v>0.13411588966846466</v>
       </c>
       <c r="C376" s="1">
-        <v>-0.23632565140724182</v>
+        <v>-0.13459771871566773</v>
       </c>
     </row>
     <row r="377">
@@ -4214,7 +4212,7 @@
         <v>-0.027595099061727524</v>
       </c>
       <c r="C377" s="1">
-        <v>0.23042041063308716</v>
+        <v>0.15450659394264221</v>
       </c>
     </row>
     <row r="378">
@@ -4225,7 +4223,7 @@
         <v>-0.42008692026138306</v>
       </c>
       <c r="C378" s="1">
-        <v>-0.030629880726337433</v>
+        <v>0.015548191033303738</v>
       </c>
     </row>
     <row r="379">
@@ -4236,7 +4234,7 @@
         <v>-0.075286142528057098</v>
       </c>
       <c r="C379" s="1">
-        <v>0.043814823031425476</v>
+        <v>0.067334763705730438</v>
       </c>
     </row>
     <row r="380">
@@ -4247,7 +4245,7 @@
         <v>-0.03965490311384201</v>
       </c>
       <c r="C380" s="1">
-        <v>0.18488346040248871</v>
+        <v>0.17867839336395264</v>
       </c>
     </row>
     <row r="381">
@@ -4258,7 +4256,7 @@
         <v>0.12753783166408539</v>
       </c>
       <c r="C381" s="1">
-        <v>0.015816887840628624</v>
+        <v>0.032078556716442108</v>
       </c>
     </row>
     <row r="382">
@@ -4269,7 +4267,7 @@
         <v>0.13082686066627502</v>
       </c>
       <c r="C382" s="1">
-        <v>0.011024747043848038</v>
+        <v>0.087315723299980164</v>
       </c>
     </row>
     <row r="383">
@@ -4280,7 +4278,7 @@
         <v>0.19002953171730042</v>
       </c>
       <c r="C383" s="1">
-        <v>0.0089739346876740456</v>
+        <v>0.0074478043243288994</v>
       </c>
     </row>
     <row r="384">
@@ -4291,7 +4289,7 @@
         <v>0.0041989265009760857</v>
       </c>
       <c r="C384" s="1">
-        <v>0.099243037402629852</v>
+        <v>0.10397424548864365</v>
       </c>
     </row>
     <row r="385">
@@ -4302,7 +4300,7 @@
         <v>0.22620894014835358</v>
       </c>
       <c r="C385" s="1">
-        <v>0.092699304223060608</v>
+        <v>0.068239383399486542</v>
       </c>
     </row>
     <row r="386">
@@ -4313,7 +4311,7 @@
         <v>0.086973041296005249</v>
       </c>
       <c r="C386" s="1">
-        <v>0.18661166727542877</v>
+        <v>0.10110028833150864</v>
       </c>
     </row>
     <row r="387">
@@ -4324,7 +4322,7 @@
         <v>-0.090086810290813446</v>
       </c>
       <c r="C387" s="1">
-        <v>0.10281354933977127</v>
+        <v>0.095018193125724792</v>
       </c>
     </row>
     <row r="388">
@@ -4335,7 +4333,7 @@
         <v>0.1291823536157608</v>
       </c>
       <c r="C388" s="1">
-        <v>0.13071580231189728</v>
+        <v>0.12455844134092331</v>
       </c>
     </row>
     <row r="389">
@@ -4346,7 +4344,7 @@
         <v>0.31391659379005432</v>
       </c>
       <c r="C389" s="1">
-        <v>-0.17501907050609589</v>
+        <v>-0.1708892434835434</v>
       </c>
     </row>
     <row r="390">
@@ -4354,10 +4352,10 @@
         <v>200705</v>
       </c>
       <c r="B390" s="1">
-        <v>0.23772056400775909</v>
+        <v>0.2377205640077591</v>
       </c>
       <c r="C390" s="1">
-        <v>0.32067948579788208</v>
+        <v>0.27600860595703125</v>
       </c>
     </row>
     <row r="391">
@@ -4368,7 +4366,7 @@
         <v>-0.0067645306698977947</v>
       </c>
       <c r="C391" s="1">
-        <v>-0.031834565103054047</v>
+        <v>0.0030747947748750448</v>
       </c>
     </row>
     <row r="392">
@@ -4379,7 +4377,7 @@
         <v>-0.26933935284614563</v>
       </c>
       <c r="C392" s="1">
-        <v>0.032965932041406631</v>
+        <v>0.025978520512580872</v>
       </c>
     </row>
     <row r="393">
@@ -4390,7 +4388,7 @@
         <v>-0.00018645422824192792</v>
       </c>
       <c r="C393" s="1">
-        <v>0.18894626200199127</v>
+        <v>0.12845759093761444</v>
       </c>
     </row>
     <row r="394">
@@ -4401,7 +4399,7 @@
         <v>0.082039475440979004</v>
       </c>
       <c r="C394" s="1">
-        <v>-0.11276119947433472</v>
+        <v>-0.12686720490455627</v>
       </c>
     </row>
     <row r="395">
@@ -4412,7 +4410,7 @@
         <v>0.12479697912931442</v>
       </c>
       <c r="C395" s="1">
-        <v>-0.062174972146749496</v>
+        <v>-0.069902710616588593</v>
       </c>
     </row>
     <row r="396">
@@ -4423,7 +4421,7 @@
         <v>-0.22000378370285034</v>
       </c>
       <c r="C396" s="1">
-        <v>-0.11622602492570877</v>
+        <v>-0.17212763428688049</v>
       </c>
     </row>
     <row r="397">
@@ -4434,7 +4432,7 @@
         <v>-0.0051200119778513908</v>
       </c>
       <c r="C397" s="1">
-        <v>0.27091383934020996</v>
+        <v>0.19564802944660187</v>
       </c>
     </row>
     <row r="398">
@@ -4445,7 +4443,7 @@
         <v>-0.68704712390899658</v>
       </c>
       <c r="C398" s="1">
-        <v>0.16235204041004181</v>
+        <v>0.15383918583393097</v>
       </c>
     </row>
     <row r="399">
@@ -4456,7 +4454,7 @@
         <v>-0.094472192227840424</v>
       </c>
       <c r="C399" s="1">
-        <v>0.016937458887696266</v>
+        <v>0.045333173125982285</v>
       </c>
     </row>
     <row r="400">
@@ -4467,7 +4465,7 @@
         <v>-0.1657346785068512</v>
       </c>
       <c r="C400" s="1">
-        <v>-0.19511605799198151</v>
+        <v>-0.14995072782039642</v>
       </c>
     </row>
     <row r="401">
@@ -4478,7 +4476,7 @@
         <v>0.22291991114616394</v>
       </c>
       <c r="C401" s="1">
-        <v>0.10628825426101685</v>
+        <v>0.047146890312433243</v>
       </c>
     </row>
     <row r="402">
@@ -4489,7 +4487,7 @@
         <v>0.072720542550086975</v>
       </c>
       <c r="C402" s="1">
-        <v>-0.12064182758331299</v>
+        <v>-0.14492961764335632</v>
       </c>
     </row>
     <row r="403">
@@ -4500,7 +4498,7 @@
         <v>-0.50669825077056885</v>
       </c>
       <c r="C403" s="1">
-        <v>0.37283006310462952</v>
+        <v>0.3001255989074707</v>
       </c>
     </row>
     <row r="404">
@@ -4511,7 +4509,7 @@
         <v>-0.084605082869529724</v>
       </c>
       <c r="C404" s="1">
-        <v>-0.14750449359416962</v>
+        <v>-0.10861522704362869</v>
       </c>
     </row>
     <row r="405">
@@ -4522,7 +4520,7 @@
         <v>-0.08405691385269165</v>
       </c>
       <c r="C405" s="1">
-        <v>0.65932947397232056</v>
+        <v>0.61195975542068481</v>
       </c>
     </row>
     <row r="406">
@@ -4533,7 +4531,7 @@
         <v>-0.47325965762138367</v>
       </c>
       <c r="C406" s="1">
-        <v>0.14195854961872101</v>
+        <v>0.17217341065406799</v>
       </c>
     </row>
     <row r="407">
@@ -4544,7 +4542,7 @@
         <v>-0.70349228382110596</v>
       </c>
       <c r="C407" s="1">
-        <v>0.19548423588275909</v>
+        <v>0.26965442299842835</v>
       </c>
     </row>
     <row r="408">
@@ -4555,7 +4553,7 @@
         <v>-0.59605038166046143</v>
       </c>
       <c r="C408" s="1">
-        <v>-0.24241244792938232</v>
+        <v>-0.061718776822090149</v>
       </c>
     </row>
     <row r="409">
@@ -4566,7 +4564,7 @@
         <v>0.084780342876911163</v>
       </c>
       <c r="C409" s="1">
-        <v>-0.73195523023605347</v>
+        <v>-0.52577835321426392</v>
       </c>
     </row>
     <row r="410">
@@ -4577,7 +4575,7 @@
         <v>-0.48477131128311157</v>
       </c>
       <c r="C410" s="1">
-        <v>-0.7985960841178894</v>
+        <v>-0.59505993127822876</v>
       </c>
     </row>
     <row r="411">
@@ -4588,7 +4586,7 @@
         <v>-0.63497066497802734</v>
       </c>
       <c r="C411" s="1">
-        <v>-0.19477066397666931</v>
+        <v>-0.11352070420980453</v>
       </c>
     </row>
     <row r="412">
@@ -4599,7 +4597,7 @@
         <v>0.24429866671562195</v>
       </c>
       <c r="C412" s="1">
-        <v>-0.34664237499237061</v>
+        <v>-0.19533410668373108</v>
       </c>
     </row>
     <row r="413">
@@ -4610,7 +4608,7 @@
         <v>0.70750480890274048</v>
       </c>
       <c r="C413" s="1">
-        <v>-0.59711301326751709</v>
+        <v>-0.54656761884689331</v>
       </c>
     </row>
     <row r="414">
@@ -4621,7 +4619,7 @@
         <v>0.15056109428405762</v>
       </c>
       <c r="C414" s="1">
-        <v>0.16545639932155609</v>
+        <v>0.15028427541255951</v>
       </c>
     </row>
     <row r="415">
@@ -4632,7 +4630,7 @@
         <v>-0.11749545484781265</v>
       </c>
       <c r="C415" s="1">
-        <v>-0.18353565037250519</v>
+        <v>-0.17295169830322266</v>
       </c>
     </row>
     <row r="416">
@@ -4643,7 +4641,7 @@
         <v>0.43615913391113281</v>
       </c>
       <c r="C416" s="1">
-        <v>-0.27969130873680115</v>
+        <v>-0.14886474609375</v>
       </c>
     </row>
     <row r="417">
@@ -4654,7 +4652,7 @@
         <v>-0.034721348434686661</v>
       </c>
       <c r="C417" s="1">
-        <v>-0.0015972912078723311</v>
+        <v>-0.0094837574288249016</v>
       </c>
     </row>
     <row r="418">
@@ -4665,7 +4663,7 @@
         <v>0.18071059882640839</v>
       </c>
       <c r="C418" s="1">
-        <v>0.33893716335296631</v>
+        <v>0.32743138074874878</v>
       </c>
     </row>
     <row r="419">
@@ -4676,7 +4674,7 @@
         <v>-0.30113339424133301</v>
       </c>
       <c r="C419" s="1">
-        <v>-0.17800331115722656</v>
+        <v>-0.10578339546918869</v>
       </c>
     </row>
     <row r="420">
@@ -4687,7 +4685,7 @@
         <v>0.14617571234703064</v>
       </c>
       <c r="C420" s="1">
-        <v>0.073335438966751099</v>
+        <v>0.079083219170570374</v>
       </c>
     </row>
     <row r="421">
@@ -4698,7 +4696,7 @@
         <v>0.24539501965045929</v>
       </c>
       <c r="C421" s="1">
-        <v>0.054566863924264908</v>
+        <v>0.046921167522668839</v>
       </c>
     </row>
     <row r="422">
@@ -4709,7 +4707,7 @@
         <v>-0.28907355666160583</v>
       </c>
       <c r="C422" s="1">
-        <v>0.34176382422447205</v>
+        <v>0.32260230183601379</v>
       </c>
     </row>
     <row r="423">
@@ -4720,7 +4718,7 @@
         <v>-0.068159893155097961</v>
       </c>
       <c r="C423" s="1">
-        <v>0.13128967583179474</v>
+        <v>0.091293454170227051</v>
       </c>
     </row>
     <row r="424">
@@ -4731,7 +4729,7 @@
         <v>0.43944820761680603</v>
       </c>
       <c r="C424" s="1">
-        <v>0.30505135655403137</v>
+        <v>0.2204916775226593</v>
       </c>
     </row>
     <row r="425">
@@ -4742,7 +4740,7 @@
         <v>-0.038558557629585266</v>
       </c>
       <c r="C425" s="1">
-        <v>0.34507760405540466</v>
+        <v>0.27663737535476685</v>
       </c>
     </row>
     <row r="426">
@@ -4753,7 +4751,7 @@
         <v>-0.18875792622566223</v>
       </c>
       <c r="C426" s="1">
-        <v>0.84663587808609009</v>
+        <v>0.68184787034988403</v>
       </c>
     </row>
     <row r="427">
@@ -4764,7 +4762,7 @@
         <v>-0.023209717124700546</v>
       </c>
       <c r="C427" s="1">
-        <v>0.3798617422580719</v>
+        <v>0.28750267624855042</v>
       </c>
     </row>
     <row r="428">
@@ -4775,7 +4773,7 @@
         <v>0.1078035980463028</v>
       </c>
       <c r="C428" s="1">
-        <v>-0.15653158724308014</v>
+        <v>-0.076527982950210571</v>
       </c>
     </row>
     <row r="429">
@@ -4786,7 +4784,7 @@
         <v>-0.20355859398841858</v>
       </c>
       <c r="C429" s="1">
-        <v>0.022200129926204681</v>
+        <v>0.054782304912805557</v>
       </c>
     </row>
     <row r="430">
@@ -4797,7 +4795,7 @@
         <v>0.26403287053108215</v>
       </c>
       <c r="C430" s="1">
-        <v>0.10876502096652985</v>
+        <v>0.10116104036569595</v>
       </c>
     </row>
     <row r="431">
@@ -4808,7 +4806,7 @@
         <v>0.24375048279762268</v>
       </c>
       <c r="C431" s="1">
-        <v>-0.18604879081249237</v>
+        <v>-0.16152319312095642</v>
       </c>
     </row>
     <row r="432">
@@ -4819,7 +4817,7 @@
         <v>0.035992957651615143</v>
       </c>
       <c r="C432" s="1">
-        <v>0.1193118691444397</v>
+        <v>0.12597744166851044</v>
       </c>
     </row>
     <row r="433">
@@ -4830,7 +4828,7 @@
         <v>0.20866742730140686</v>
       </c>
       <c r="C433" s="1">
-        <v>0.42567676305770874</v>
+        <v>0.33379647135734558</v>
       </c>
     </row>
     <row r="434">
@@ -4841,7 +4839,7 @@
         <v>0.00036171774263493717</v>
       </c>
       <c r="C434" s="1">
-        <v>-0.031215451657772064</v>
+        <v>-0.052516158670186996</v>
       </c>
     </row>
     <row r="435">
@@ -4852,7 +4850,7 @@
         <v>0.066142462193965912</v>
       </c>
       <c r="C435" s="1">
-        <v>0.082941330969333649</v>
+        <v>0.088591940701007843</v>
       </c>
     </row>
     <row r="436">
@@ -4863,7 +4861,7 @@
         <v>-0.15038582682609558</v>
       </c>
       <c r="C436" s="1">
-        <v>0.21673716604709625</v>
+        <v>0.13596521317958832</v>
       </c>
     </row>
     <row r="437">
@@ -4874,7 +4872,7 @@
         <v>0.23169068992137909</v>
       </c>
       <c r="C437" s="1">
-        <v>-0.053216211497783661</v>
+        <v>-0.066444829106330872</v>
       </c>
     </row>
     <row r="438">
@@ -4885,7 +4883,7 @@
         <v>-0.1460004448890686</v>
       </c>
       <c r="C438" s="1">
-        <v>0.079797722399234772</v>
+        <v>0.10221198201179504</v>
       </c>
     </row>
     <row r="439">
@@ -4896,7 +4894,7 @@
         <v>-0.030884137377142906</v>
       </c>
       <c r="C439" s="1">
-        <v>-0.074068062007427216</v>
+        <v>0.0029017175547778606</v>
       </c>
     </row>
     <row r="440">
@@ -4907,7 +4905,7 @@
         <v>-0.19752870500087738</v>
       </c>
       <c r="C440" s="1">
-        <v>0.30056890845298767</v>
+        <v>0.2841276228427887</v>
       </c>
     </row>
     <row r="441">
@@ -4918,7 +4916,7 @@
         <v>-0.89590096473693848</v>
       </c>
       <c r="C441" s="1">
-        <v>0.12066253274679184</v>
+        <v>0.16796252131462097</v>
       </c>
     </row>
     <row r="442">
@@ -4929,7 +4927,7 @@
         <v>-0.3839074969291687</v>
       </c>
       <c r="C442" s="1">
-        <v>0.013790605589747429</v>
+        <v>0.012818537652492523</v>
       </c>
     </row>
     <row r="443">
@@ -4940,7 +4938,7 @@
         <v>0.54360103607177734</v>
       </c>
       <c r="C443" s="1">
-        <v>0.27903267741203308</v>
+        <v>0.17484025657176972</v>
       </c>
     </row>
     <row r="444">
@@ -4951,7 +4949,7 @@
         <v>-0.1224290132522583</v>
       </c>
       <c r="C444" s="1">
-        <v>0.12535226345062256</v>
+        <v>0.12012943625450134</v>
       </c>
     </row>
     <row r="445">
@@ -4962,7 +4960,7 @@
         <v>-0.18272803723812103</v>
       </c>
       <c r="C445" s="1">
-        <v>-0.012628871947526932</v>
+        <v>0.067079335451126099</v>
       </c>
     </row>
     <row r="446">
@@ -4973,7 +4971,7 @@
         <v>0.44492989778518677</v>
       </c>
       <c r="C446" s="1">
-        <v>0.21287219226360321</v>
+        <v>0.13104173541069031</v>
       </c>
     </row>
     <row r="447">
@@ -4984,7 +4982,7 @@
         <v>0.26403287053108215</v>
       </c>
       <c r="C447" s="1">
-        <v>-0.20348185300827026</v>
+        <v>-0.20493543148040771</v>
       </c>
     </row>
     <row r="448">
@@ -4995,7 +4993,7 @@
         <v>0.011325177736580372</v>
       </c>
       <c r="C448" s="1">
-        <v>0.0035425592213869095</v>
+        <v>-0.019797390326857567</v>
       </c>
     </row>
     <row r="449">
@@ -5006,7 +5004,7 @@
         <v>-0.11530276387929916</v>
       </c>
       <c r="C449" s="1">
-        <v>-0.11354121565818787</v>
+        <v>-0.11215345561504364</v>
       </c>
     </row>
     <row r="450">
@@ -5017,7 +5015,7 @@
         <v>-0.40035268664360046</v>
       </c>
       <c r="C450" s="1">
-        <v>0.36363467574119568</v>
+        <v>0.2937375009059906</v>
       </c>
     </row>
     <row r="451">
@@ -5028,7 +5026,7 @@
         <v>0.020644115284085274</v>
       </c>
       <c r="C451" s="1">
-        <v>-0.093101732432842255</v>
+        <v>-0.01009481493383646</v>
       </c>
     </row>
     <row r="452">
@@ -5039,7 +5037,7 @@
         <v>0.21360097825527191</v>
       </c>
       <c r="C452" s="1">
-        <v>0.073953092098236084</v>
+        <v>0.065270736813545227</v>
       </c>
     </row>
     <row r="453">
@@ -5050,7 +5048,7 @@
         <v>0.065046109259128571</v>
       </c>
       <c r="C453" s="1">
-        <v>0.094152703881263733</v>
+        <v>0.065793834626674652</v>
       </c>
     </row>
     <row r="454">
@@ -5061,7 +5059,7 @@
         <v>0.11712253838777542</v>
       </c>
       <c r="C454" s="1">
-        <v>-0.40993320941925049</v>
+        <v>-0.34989500045776367</v>
       </c>
     </row>
     <row r="455">
@@ -5072,7 +5070,7 @@
         <v>0.02941487729549408</v>
       </c>
       <c r="C455" s="1">
-        <v>-0.27170035243034363</v>
+        <v>-0.19466009736061096</v>
       </c>
     </row>
     <row r="456">
@@ -5083,7 +5081,7 @@
         <v>0.071624197065830231</v>
       </c>
       <c r="C456" s="1">
-        <v>-0.019510619342327118</v>
+        <v>-0.04330502450466156</v>
       </c>
     </row>
     <row r="457">
@@ -5094,7 +5092,7 @@
         <v>0.083683997392654419</v>
       </c>
       <c r="C457" s="1">
-        <v>-0.069552391767501831</v>
+        <v>-0.089984357357025147</v>
       </c>
     </row>
     <row r="458">
@@ -5105,7 +5103,7 @@
         <v>0.11876705288887024</v>
       </c>
       <c r="C458" s="1">
-        <v>-0.4768848717212677</v>
+        <v>-0.38245546817779541</v>
       </c>
     </row>
     <row r="459">
@@ -5116,7 +5114,7 @@
         <v>-0.039106730371713638</v>
       </c>
       <c r="C459" s="1">
-        <v>-0.02638145349919796</v>
+        <v>-0.024785410612821579</v>
       </c>
     </row>
     <row r="460">
@@ -5127,7 +5125,7 @@
         <v>-0.037462212145328522</v>
       </c>
       <c r="C460" s="1">
-        <v>0.55912333726882935</v>
+        <v>0.43471705913543701</v>
       </c>
     </row>
     <row r="461">
@@ -5138,7 +5136,7 @@
         <v>0.0085843075066804886</v>
       </c>
       <c r="C461" s="1">
-        <v>-0.12495142966508865</v>
+        <v>-0.073680013418197632</v>
       </c>
     </row>
     <row r="462">
@@ -5149,7 +5147,7 @@
         <v>0.21853451430797577</v>
       </c>
       <c r="C462" s="1">
-        <v>-0.17094339430332184</v>
+        <v>-0.15334196388721466</v>
       </c>
     </row>
     <row r="463">
@@ -5160,7 +5158,7 @@
         <v>-0.24357521533966064</v>
       </c>
       <c r="C463" s="1">
-        <v>0.2642102837562561</v>
+        <v>0.23547454178333283</v>
       </c>
     </row>
     <row r="464">
@@ -5171,7 +5169,7 @@
         <v>0.1785178929567337</v>
       </c>
       <c r="C464" s="1">
-        <v>-0.22375676035881042</v>
+        <v>-0.17671863734722138</v>
       </c>
     </row>
     <row r="465">
@@ -5182,7 +5180,7 @@
         <v>-0.11804362386465073</v>
       </c>
       <c r="C465" s="1">
-        <v>0.038306150585412979</v>
+        <v>0.096990667283535004</v>
       </c>
     </row>
     <row r="466">
@@ -5193,7 +5191,7 @@
         <v>0.23662422597408295</v>
       </c>
       <c r="C466" s="1">
-        <v>-0.1552162766456604</v>
+        <v>-0.12535716593265533</v>
       </c>
     </row>
     <row r="467">
@@ -5201,10 +5199,10 @@
         <v>201310</v>
       </c>
       <c r="B467" s="1">
-        <v>0.23388336598873138</v>
+        <v>0.23388336598873139</v>
       </c>
       <c r="C467" s="1">
-        <v>-0.064707830548286438</v>
+        <v>0.011500714346766472</v>
       </c>
     </row>
     <row r="468">
@@ -5215,7 +5213,7 @@
         <v>0.15056109428405762</v>
       </c>
       <c r="C468" s="1">
-        <v>0.12426730990409851</v>
+        <v>0.1084294319152832</v>
       </c>
     </row>
     <row r="469">
@@ -5226,7 +5224,7 @@
         <v>0.030511220917105675</v>
       </c>
       <c r="C469" s="1">
-        <v>-0.38001167774200439</v>
+        <v>-0.28262412548065186</v>
       </c>
     </row>
     <row r="470">
@@ -5237,7 +5235,7 @@
         <v>-0.16847553849220276</v>
       </c>
       <c r="C470" s="1">
-        <v>0.12084688246250153</v>
+        <v>0.1356329470872879</v>
       </c>
     </row>
     <row r="471">
@@ -5248,7 +5246,7 @@
         <v>0.13411588966846466</v>
       </c>
       <c r="C471" s="1">
-        <v>-0.11712139844894409</v>
+        <v>-0.089454561471939087</v>
       </c>
     </row>
     <row r="472">
@@ -5259,7 +5257,7 @@
         <v>-0.086797773838043213</v>
       </c>
       <c r="C472" s="1">
-        <v>-0.017628245055675507</v>
+        <v>-0.037920478731393814</v>
       </c>
     </row>
     <row r="473">
@@ -5270,7 +5268,7 @@
         <v>-0.03965490311384201</v>
       </c>
       <c r="C473" s="1">
-        <v>-0.1141945943236351</v>
+        <v>-0.061337411403656006</v>
       </c>
     </row>
     <row r="474">
@@ -5281,7 +5279,7 @@
         <v>0.14727206528186798</v>
       </c>
       <c r="C474" s="1">
-        <v>0.10702113807201385</v>
+        <v>0.14278887212276459</v>
       </c>
     </row>
     <row r="475">
@@ -5289,10 +5287,10 @@
         <v>201406</v>
       </c>
       <c r="B475" s="1">
-        <v>-0.09118315577507019</v>
+        <v>-0.091183155775070191</v>
       </c>
       <c r="C475" s="1">
-        <v>-0.013707464560866356</v>
+        <v>0.024328755214810371</v>
       </c>
     </row>
     <row r="476">
@@ -5303,7 +5301,7 @@
         <v>-0.29729616641998291</v>
       </c>
       <c r="C476" s="1">
-        <v>0.1382049024105072</v>
+        <v>0.14013797044754028</v>
       </c>
     </row>
     <row r="477">
@@ -5314,7 +5312,7 @@
         <v>-0.0067645306698977947</v>
       </c>
       <c r="C477" s="1">
-        <v>-0.3620699942111969</v>
+        <v>-0.2621690034866333</v>
       </c>
     </row>
     <row r="478">
@@ -5325,7 +5323,7 @@
         <v>-0.082960560917854309</v>
       </c>
       <c r="C478" s="1">
-        <v>0.33956092596054077</v>
+        <v>0.31503570079803467</v>
       </c>
     </row>
     <row r="479">
@@ -5336,7 +5334,7 @@
         <v>-0.086797773838043213</v>
       </c>
       <c r="C479" s="1">
-        <v>0.044083572924137115</v>
+        <v>0.12243205308914185</v>
       </c>
     </row>
     <row r="480">
@@ -5347,7 +5345,7 @@
         <v>0.27938172221183777</v>
       </c>
       <c r="C480" s="1">
-        <v>0.18762122094631195</v>
+        <v>0.20367881655693054</v>
       </c>
     </row>
     <row r="481">
@@ -5358,7 +5356,7 @@
         <v>-0.07035258412361145</v>
       </c>
       <c r="C481" s="1">
-        <v>0.15750832855701447</v>
+        <v>0.23009483516216278</v>
       </c>
     </row>
     <row r="482">
@@ -5369,7 +5367,7 @@
         <v>0.39011266827583313</v>
       </c>
       <c r="C482" s="1">
-        <v>0.16750282049179077</v>
+        <v>0.23933833837509155</v>
       </c>
     </row>
     <row r="483">
@@ -5380,7 +5378,7 @@
         <v>0.31007939577102661</v>
       </c>
       <c r="C483" s="1">
-        <v>0.11008861660957336</v>
+        <v>0.071260623633861542</v>
       </c>
     </row>
     <row r="484">
@@ -5391,7 +5389,7 @@
         <v>0.19386674463748932</v>
       </c>
       <c r="C484" s="1">
-        <v>0.14543934166431427</v>
+        <v>0.10984724760055542</v>
       </c>
     </row>
     <row r="485">
@@ -5402,7 +5400,7 @@
         <v>-0.24741242825984955</v>
       </c>
       <c r="C485" s="1">
-        <v>0.2672676146030426</v>
+        <v>0.25648036599159241</v>
       </c>
     </row>
     <row r="486">
@@ -5413,7 +5411,7 @@
         <v>0.0058434475213289261</v>
       </c>
       <c r="C486" s="1">
-        <v>-0.22394146025180817</v>
+        <v>-0.17680200934410095</v>
       </c>
     </row>
     <row r="487">
@@ -5424,7 +5422,7 @@
         <v>-0.24467155337333679</v>
       </c>
       <c r="C487" s="1">
-        <v>-0.093937456607818604</v>
+        <v>-0.0016539552016183734</v>
       </c>
     </row>
     <row r="488">
@@ -5435,7 +5433,7 @@
         <v>0.090810246765613556</v>
       </c>
       <c r="C488" s="1">
-        <v>0.39902764558792114</v>
+        <v>0.38629329204559326</v>
       </c>
     </row>
     <row r="489">
@@ -5446,7 +5444,7 @@
         <v>-0.46887427568435669</v>
       </c>
       <c r="C489" s="1">
-        <v>-0.25165286660194397</v>
+        <v>-0.21020187437534332</v>
       </c>
     </row>
     <row r="490">
@@ -5457,7 +5455,7 @@
         <v>-0.33731278777122498</v>
       </c>
       <c r="C490" s="1">
-        <v>-0.06758735328912735</v>
+        <v>0.023819470778107643</v>
       </c>
     </row>
     <row r="491">
@@ -5468,7 +5466,7 @@
         <v>0.51071071624755859</v>
       </c>
       <c r="C491" s="1">
-        <v>-0.06142837181687355</v>
+        <v>-0.04601457342505455</v>
       </c>
     </row>
     <row r="492">
@@ -5479,7 +5477,7 @@
         <v>0.1823551207780838</v>
       </c>
       <c r="C492" s="1">
-        <v>0.26676613092422485</v>
+        <v>0.22546279430389404</v>
       </c>
     </row>
     <row r="493">
@@ -5490,7 +5488,7 @@
         <v>-0.25673136115074158</v>
       </c>
       <c r="C493" s="1">
-        <v>-0.085839658975601196</v>
+        <v>0.039472311735153198</v>
       </c>
     </row>
     <row r="494">
@@ -5501,7 +5499,7 @@
         <v>-0.47490417957305908</v>
       </c>
       <c r="C494" s="1">
-        <v>0.14225731790065765</v>
+        <v>0.2029661238193512</v>
       </c>
     </row>
     <row r="495">
@@ -5512,7 +5510,7 @@
         <v>-0.2090403288602829</v>
       </c>
       <c r="C495" s="1">
-        <v>0.15981359779834747</v>
+        <v>0.10935398191213608</v>
       </c>
     </row>
     <row r="496">
@@ -5523,7 +5521,7 @@
         <v>0.21798636019229889</v>
       </c>
       <c r="C496" s="1">
-        <v>-0.20547689497470856</v>
+        <v>-0.16754727065563202</v>
       </c>
     </row>
     <row r="497">
@@ -5534,7 +5532,7 @@
         <v>0.0085843075066804886</v>
       </c>
       <c r="C497" s="1">
-        <v>0.15671755373477936</v>
+        <v>0.13347417116165161</v>
       </c>
     </row>
     <row r="498">
@@ -5545,7 +5543,7 @@
         <v>0.068883322179317474</v>
       </c>
       <c r="C498" s="1">
-        <v>-0.24177564680576324</v>
+        <v>-0.17105899751186371</v>
       </c>
     </row>
     <row r="499">
@@ -5556,7 +5554,7 @@
         <v>-0.3033260703086853</v>
       </c>
       <c r="C499" s="1">
-        <v>0.16727644205093384</v>
+        <v>0.1800604909658432</v>
       </c>
     </row>
     <row r="500">
@@ -5567,7 +5565,7 @@
         <v>0.26458105444908142</v>
       </c>
       <c r="C500" s="1">
-        <v>0.20421147346496582</v>
+        <v>0.12894430756568909</v>
       </c>
     </row>
     <row r="501">
@@ -5578,7 +5576,7 @@
         <v>0.050793621689081192</v>
       </c>
       <c r="C501" s="1">
-        <v>0.085424624383449554</v>
+        <v>0.039159853011369705</v>
       </c>
     </row>
     <row r="502">
@@ -5589,7 +5587,7 @@
         <v>-0.048973843455314636</v>
       </c>
       <c r="C502" s="1">
-        <v>0.17259418964385986</v>
+        <v>0.15211696922779083</v>
       </c>
     </row>
     <row r="503">
@@ -5600,7 +5598,7 @@
         <v>-0.022661546245217323</v>
       </c>
       <c r="C503" s="1">
-        <v>0.073817938566207886</v>
+        <v>0.074855580925941467</v>
       </c>
     </row>
     <row r="504">
@@ -5611,7 +5609,7 @@
         <v>-0.099953919649124146</v>
       </c>
       <c r="C504" s="1">
-        <v>0.30916538834571838</v>
+        <v>0.28699645400047302</v>
       </c>
     </row>
     <row r="505">
@@ -5622,7 +5620,7 @@
         <v>0.33803623914718628</v>
       </c>
       <c r="C505" s="1">
-        <v>-0.23824729025363922</v>
+        <v>-0.23048490285873413</v>
       </c>
     </row>
     <row r="506">
@@ -5633,7 +5631,7 @@
         <v>0.033800262957811356</v>
       </c>
       <c r="C506" s="1">
-        <v>0.043697576969861984</v>
+        <v>0.061277322471141815</v>
       </c>
     </row>
     <row r="507">
@@ -5644,7 +5642,7 @@
         <v>0.060112565755844116</v>
       </c>
       <c r="C507" s="1">
-        <v>-0.02291182242333889</v>
+        <v>-0.010584668256342411</v>
       </c>
     </row>
     <row r="508">
@@ -5655,7 +5653,7 @@
         <v>0.14343485236167908</v>
       </c>
       <c r="C508" s="1">
-        <v>-0.17176057398319244</v>
+        <v>-0.083518795669078827</v>
       </c>
     </row>
     <row r="509">
@@ -5666,7 +5664,7 @@
         <v>0.044215545058250427</v>
       </c>
       <c r="C509" s="1">
-        <v>0.38993984460830688</v>
+        <v>0.34210798144340515</v>
       </c>
     </row>
     <row r="510">
@@ -5677,7 +5675,7 @@
         <v>0.081491298973560333</v>
       </c>
       <c r="C510" s="1">
-        <v>-0.13521714508533478</v>
+        <v>-0.14468660950660706</v>
       </c>
     </row>
     <row r="511">
@@ -5688,7 +5686,7 @@
         <v>-0.17286092042922974</v>
       </c>
       <c r="C511" s="1">
-        <v>-0.16648757457733154</v>
+        <v>-0.10113111138343811</v>
       </c>
     </row>
     <row r="512">
@@ -5699,7 +5697,7 @@
         <v>-0.085701428353786469</v>
       </c>
       <c r="C512" s="1">
-        <v>0.15369351208209991</v>
+        <v>0.15242241322994232</v>
       </c>
     </row>
     <row r="513">
@@ -5710,7 +5708,7 @@
         <v>-0.046232979744672775</v>
       </c>
       <c r="C513" s="1">
-        <v>0.028219668194651604</v>
+        <v>0.032482098788022995</v>
       </c>
     </row>
     <row r="514">
@@ -5721,7 +5719,7 @@
         <v>0.2552621066570282</v>
       </c>
       <c r="C514" s="1">
-        <v>-0.25842905044555664</v>
+        <v>-0.19500903785228729</v>
       </c>
     </row>
     <row r="515">
@@ -5732,7 +5730,7 @@
         <v>0.14014580845832825</v>
       </c>
       <c r="C515" s="1">
-        <v>-0.18221437931060791</v>
+        <v>-0.089130103588104248</v>
       </c>
     </row>
     <row r="516">
@@ -5740,10 +5738,10 @@
         <v>201711</v>
       </c>
       <c r="B516" s="1">
-        <v>-0.1026947870850563</v>
+        <v>-0.10269478708505631</v>
       </c>
       <c r="C516" s="1">
-        <v>0.60557126998901367</v>
+        <v>0.45550847053527832</v>
       </c>
     </row>
     <row r="517">
@@ -5754,7 +5752,7 @@
         <v>-0.067063547670841217</v>
       </c>
       <c r="C517" s="1">
-        <v>-0.18946473300457001</v>
+        <v>-0.14068073034286499</v>
       </c>
     </row>
     <row r="518">
@@ -5765,7 +5763,7 @@
         <v>0.075461402535438538</v>
       </c>
       <c r="C518" s="1">
-        <v>0.014652442187070847</v>
+        <v>0.030795831233263016</v>
       </c>
     </row>
     <row r="519">
@@ -5776,7 +5774,7 @@
         <v>-0.30277788639068604</v>
       </c>
       <c r="C519" s="1">
-        <v>-0.18878988921642303</v>
+        <v>-0.16697207093238831</v>
       </c>
     </row>
     <row r="520">
@@ -5784,10 +5782,10 @@
         <v>201803</v>
       </c>
       <c r="B520" s="1">
-        <v>-0.14709679782390594</v>
+        <v>-0.14709679782390595</v>
       </c>
       <c r="C520" s="1">
-        <v>0.094460777938365936</v>
+        <v>0.11293252557516098</v>
       </c>
     </row>
     <row r="521">
@@ -5798,7 +5796,7 @@
         <v>0.12205609679222107</v>
       </c>
       <c r="C521" s="1">
-        <v>-0.1396109014749527</v>
+        <v>-0.10696518421173096</v>
       </c>
     </row>
     <row r="522">
@@ -5809,7 +5807,7 @@
         <v>-0.012246260419487953</v>
       </c>
       <c r="C522" s="1">
-        <v>0.599678635597229</v>
+        <v>0.47056683897972107</v>
       </c>
     </row>
     <row r="523">
@@ -5820,7 +5818,7 @@
         <v>-0.21945562958717346</v>
       </c>
       <c r="C523" s="1">
-        <v>-0.033394835889339447</v>
+        <v>0.014025431126356125</v>
       </c>
     </row>
     <row r="524">
@@ -5831,7 +5829,7 @@
         <v>0.1549464613199234</v>
       </c>
       <c r="C524" s="1">
-        <v>-0.19234378635883331</v>
+        <v>-0.18982017040252686</v>
       </c>
     </row>
     <row r="525">
@@ -5842,7 +5840,7 @@
         <v>-0.14435592293739319</v>
       </c>
       <c r="C525" s="1">
-        <v>0.12998157739639282</v>
+        <v>0.10929094254970551</v>
       </c>
     </row>
     <row r="526">
@@ -5853,7 +5851,7 @@
         <v>-0.14928948879241943</v>
       </c>
       <c r="C526" s="1">
-        <v>-0.24033382534980774</v>
+        <v>-0.21230243146419525</v>
       </c>
     </row>
     <row r="527">
@@ -5864,7 +5862,7 @@
         <v>-0.38007029891014099</v>
       </c>
       <c r="C527" s="1">
-        <v>0.35581731796264648</v>
+        <v>0.32056459784507751</v>
       </c>
     </row>
     <row r="528">
@@ -5875,7 +5873,7 @@
         <v>-0.13065160810947418</v>
       </c>
       <c r="C528" s="1">
-        <v>-0.204456627368927</v>
+        <v>-0.12928502261638641</v>
       </c>
     </row>
     <row r="529">
@@ -5886,7 +5884,7 @@
         <v>-0.40309351682662964</v>
       </c>
       <c r="C529" s="1">
-        <v>0.066574864089488983</v>
+        <v>0.17045910656452179</v>
       </c>
     </row>
     <row r="530">
@@ -5897,7 +5895,7 @@
         <v>0.28047806024551392</v>
       </c>
       <c r="C530" s="1">
-        <v>-0.16306260228157043</v>
+        <v>-0.083260118961334229</v>
       </c>
     </row>
     <row r="531">
@@ -5908,7 +5906,7 @@
         <v>0.067786984145641327</v>
       </c>
       <c r="C531" s="1">
-        <v>0.23956474661827087</v>
+        <v>0.22013546526432037</v>
       </c>
     </row>
     <row r="532">
@@ -5919,7 +5917,7 @@
         <v>-0.040751248598098755</v>
       </c>
       <c r="C532" s="1">
-        <v>0.045163773000240326</v>
+        <v>0.051515262573957443</v>
       </c>
     </row>
     <row r="533">
@@ -5930,7 +5928,7 @@
         <v>0.31775379180908203</v>
       </c>
       <c r="C533" s="1">
-        <v>-0.23500353097915649</v>
+        <v>-0.24420289695262909</v>
       </c>
     </row>
     <row r="534">
@@ -5941,7 +5939,7 @@
         <v>-0.35211345553398132</v>
       </c>
       <c r="C534" s="1">
-        <v>0.38280662894248962</v>
+        <v>0.33945354819297791</v>
       </c>
     </row>
     <row r="535">
@@ -5952,7 +5950,7 @@
         <v>0.20263752341270447</v>
       </c>
       <c r="C535" s="1">
-        <v>-0.19200438261032104</v>
+        <v>-0.19323301315307617</v>
       </c>
     </row>
     <row r="536">
@@ -5963,7 +5961,7 @@
         <v>-0.12571804225444794</v>
       </c>
       <c r="C536" s="1">
-        <v>-0.07376784086227417</v>
+        <v>-0.023600053042173386</v>
       </c>
     </row>
     <row r="537">
@@ -5974,7 +5972,7 @@
         <v>-0.11639910936355591</v>
       </c>
       <c r="C537" s="1">
-        <v>0.006610148586332798</v>
+        <v>0.041547037661075592</v>
       </c>
     </row>
     <row r="538">
@@ -5985,7 +5983,7 @@
         <v>0.10999629646539688</v>
       </c>
       <c r="C538" s="1">
-        <v>-0.14045047760009766</v>
+        <v>-0.088479653000831604</v>
       </c>
     </row>
     <row r="539">
@@ -5996,7 +5994,7 @@
         <v>0.13795313239097595</v>
       </c>
       <c r="C539" s="1">
-        <v>-0.56218266487121582</v>
+        <v>-0.43345227837562561</v>
       </c>
     </row>
     <row r="540">
@@ -6007,7 +6005,7 @@
         <v>0.12424879521131516</v>
       </c>
       <c r="C540" s="1">
-        <v>-0.43733873963356018</v>
+        <v>-0.3305145800113678</v>
       </c>
     </row>
     <row r="541">
@@ -6018,7 +6016,7 @@
         <v>-0.0034754911903291941</v>
       </c>
       <c r="C541" s="1">
-        <v>-0.34726664423942566</v>
+        <v>-0.27076306939125061</v>
       </c>
     </row>
     <row r="542">
@@ -6029,7 +6027,7 @@
         <v>-0.17505361139774323</v>
       </c>
       <c r="C542" s="1">
-        <v>-0.11023446172475815</v>
+        <v>-0.050029236823320389</v>
       </c>
     </row>
     <row r="543">
@@ -6040,7 +6038,7 @@
         <v>-0.44091746211051941</v>
       </c>
       <c r="C543" s="1">
-        <v>-0.23285119235515594</v>
+        <v>-0.1354692131280899</v>
       </c>
     </row>
     <row r="544">
@@ -6051,7 +6049,7 @@
         <v>-0.89041918516159058</v>
       </c>
       <c r="C544" s="1">
-        <v>-1.4102500677108765</v>
+        <v>-1.0417112112045288</v>
       </c>
     </row>
     <row r="545">
@@ -6062,7 +6060,7 @@
         <v>0.54140836000442505</v>
       </c>
       <c r="C545" s="1">
-        <v>-2.4655196666717529</v>
+        <v>-2.0539968013763428</v>
       </c>
     </row>
     <row r="546">
@@ -6073,7 +6071,7 @@
         <v>0.35777044296264648</v>
       </c>
       <c r="C546" s="1">
-        <v>0.75966387987136841</v>
+        <v>0.57656151056289673</v>
       </c>
     </row>
     <row r="547">
@@ -6084,7 +6082,7 @@
         <v>0.21963086724281311</v>
       </c>
       <c r="C547" s="1">
-        <v>0.59724074602127075</v>
+        <v>0.48288047313690186</v>
       </c>
     </row>
     <row r="548">
@@ -6095,7 +6093,7 @@
         <v>-0.079123355448246002</v>
       </c>
       <c r="C548" s="1">
-        <v>-0.25127333402633667</v>
+        <v>0.0044605103321373463</v>
       </c>
     </row>
     <row r="549">
@@ -6106,7 +6104,7 @@
         <v>0.23004615306854248</v>
       </c>
       <c r="C549" s="1">
-        <v>-0.56653839349746704</v>
+        <v>-0.46489274501800537</v>
       </c>
     </row>
     <row r="550">
@@ -6117,7 +6115,7 @@
         <v>-0.10543564707040787</v>
       </c>
       <c r="C550" s="1">
-        <v>0.20301884412765503</v>
+        <v>0.23496855795383453</v>
       </c>
     </row>
     <row r="551">
@@ -6128,7 +6126,7 @@
         <v>-0.43050217628479004</v>
       </c>
       <c r="C551" s="1">
-        <v>0.35594978928565979</v>
+        <v>0.32081913948059082</v>
       </c>
     </row>
     <row r="552">
@@ -6139,7 +6137,7 @@
         <v>0.66091001033782959</v>
       </c>
       <c r="C552" s="1">
-        <v>-0.065861687064170837</v>
+        <v>-0.057438220828771591</v>
       </c>
     </row>
     <row r="553">
@@ -6150,7 +6148,7 @@
         <v>0.14946474134922028</v>
       </c>
       <c r="C553" s="1">
-        <v>-0.25212582945823669</v>
+        <v>-0.18828809261322022</v>
       </c>
     </row>
     <row r="554">
@@ -6161,7 +6159,7 @@
         <v>-0.013890775851905346</v>
       </c>
       <c r="C554" s="1">
-        <v>-0.035530317574739456</v>
+        <v>-0.22977040708065033</v>
       </c>
     </row>
     <row r="555">
@@ -6172,7 +6170,7 @@
         <v>0.077105924487113953</v>
       </c>
       <c r="C555" s="1">
-        <v>-0.28189757466316223</v>
+        <v>-0.25603151321411133</v>
       </c>
     </row>
     <row r="556">
@@ -6180,10 +6178,10 @@
         <v>202103</v>
       </c>
       <c r="B556" s="1">
-        <v>0.35448139905929565</v>
+        <v>0.35448139905929566</v>
       </c>
       <c r="C556" s="1">
-        <v>0.14112839102745056</v>
+        <v>0.11195419728755951</v>
       </c>
     </row>
     <row r="557">
@@ -6194,7 +6192,7 @@
         <v>0.052438147366046906</v>
       </c>
       <c r="C557" s="1">
-        <v>0.16516810655593872</v>
+        <v>0.14098909497261047</v>
       </c>
     </row>
     <row r="558">
@@ -6205,7 +6203,7 @@
         <v>0.090262070298194885</v>
       </c>
       <c r="C558" s="1">
-        <v>-0.30504605174064636</v>
+        <v>-0.24365256726741791</v>
       </c>
     </row>
     <row r="559">
@@ -6216,7 +6214,7 @@
         <v>0.027222190052270889</v>
       </c>
       <c r="C559" s="1">
-        <v>0.36543992161750793</v>
+        <v>0.27131077647209168</v>
       </c>
     </row>
     <row r="560">
@@ -6227,7 +6225,7 @@
         <v>0.017903251573443413</v>
       </c>
       <c r="C560" s="1">
-        <v>0.50012838840484619</v>
+        <v>0.38469690084457397</v>
       </c>
     </row>
     <row r="561">
@@ -6238,7 +6236,7 @@
         <v>0.077654100954532623</v>
       </c>
       <c r="C561" s="1">
-        <v>-0.2679578959941864</v>
+        <v>-0.22807462513446808</v>
       </c>
     </row>
     <row r="562">
@@ -6246,10 +6244,10 @@
         <v>202109</v>
       </c>
       <c r="B562" s="1">
-        <v>-0.25399050116539001</v>
+        <v>-0.25399050116539002</v>
       </c>
       <c r="C562" s="1">
-        <v>-0.005369928665459156</v>
+        <v>0.019494064152240753</v>
       </c>
     </row>
     <row r="563">
@@ -6260,7 +6258,7 @@
         <v>0.055179007351398468</v>
       </c>
       <c r="C563" s="1">
-        <v>0.67725646495819092</v>
+        <v>0.49268966913223267</v>
       </c>
     </row>
     <row r="564">
@@ -6271,7 +6269,7 @@
         <v>-0.1854688972234726</v>
       </c>
       <c r="C564" s="1">
-        <v>0.10330095887184143</v>
+        <v>0.073638826608657837</v>
       </c>
     </row>
     <row r="565">
@@ -6282,7 +6280,7 @@
         <v>0.1116408184170723</v>
       </c>
       <c r="C565" s="1">
-        <v>0.40508940815925598</v>
+        <v>0.33640077710151672</v>
       </c>
     </row>
     <row r="566">
@@ -6290,10 +6288,10 @@
         <v>202201</v>
       </c>
       <c r="B566" s="1">
-        <v>-0.26440578699111938</v>
+        <v>-0.26440578699111939</v>
       </c>
       <c r="C566" s="1">
-        <v>-0.074542611837387085</v>
+        <v>-0.12064407765865326</v>
       </c>
     </row>
     <row r="567">
@@ -6304,7 +6302,7 @@
         <v>-0.43762841820716858</v>
       </c>
       <c r="C567" s="1">
-        <v>0.31824985146522522</v>
+        <v>0.20619645714759827</v>
       </c>
     </row>
     <row r="568">
@@ -6315,7 +6313,7 @@
         <v>-0.073641620576381683</v>
       </c>
       <c r="C568" s="1">
-        <v>-0.42822489142417908</v>
+        <v>-0.57679092884063721</v>
       </c>
     </row>
     <row r="569">
@@ -6326,7 +6324,7 @@
         <v>-0.22438916563987732</v>
       </c>
       <c r="C569" s="1">
-        <v>0.59959274530410767</v>
+        <v>0.44761788845062256</v>
       </c>
     </row>
     <row r="570">
@@ -6337,7 +6335,7 @@
         <v>0.13247138261795044</v>
       </c>
       <c r="C570" s="1">
-        <v>0.078076638281345367</v>
+        <v>-0.056462045758962631</v>
       </c>
     </row>
     <row r="571">
@@ -6348,7 +6346,7 @@
         <v>-0.70020323991775513</v>
       </c>
       <c r="C571" s="1">
-        <v>0.17958809435367584</v>
+        <v>0.15378352999687195</v>
       </c>
     </row>
     <row r="572">
@@ -6359,7 +6357,7 @@
         <v>0.28486344218254089</v>
       </c>
       <c r="C572" s="1">
-        <v>0.043350435793399811</v>
+        <v>-0.007063649594783783</v>
       </c>
     </row>
     <row r="573">
@@ -6370,7 +6368,7 @@
         <v>-0.35375797748565674</v>
       </c>
       <c r="C573" s="1">
-        <v>-0.13302753865718842</v>
+        <v>-0.12518225610256195</v>
       </c>
     </row>
     <row r="574">
@@ -6381,7 +6379,7 @@
         <v>-0.55877465009689331</v>
       </c>
       <c r="C574" s="1">
-        <v>-0.066294409334659576</v>
+        <v>-0.29486095905303955</v>
       </c>
     </row>
     <row r="575">
@@ -6392,7 +6390,7 @@
         <v>0.40984690189361572</v>
       </c>
       <c r="C575" s="1">
-        <v>-0.21339087188243866</v>
+        <v>-0.28782713413238525</v>
       </c>
     </row>
     <row r="576">
@@ -6403,7 +6401,7 @@
         <v>0.46685686707496643</v>
       </c>
       <c r="C576" s="1">
-        <v>0.13977405428886414</v>
+        <v>0.051998704671859741</v>
       </c>
     </row>
     <row r="577">
@@ -6414,7 +6412,7 @@
         <v>-0.279754638671875</v>
       </c>
       <c r="C577" s="1">
-        <v>-0.48052287101745605</v>
+        <v>-0.24333585798740387</v>
       </c>
     </row>
     <row r="578">
@@ -6425,7 +6423,7 @@
         <v>0.4597305953502655</v>
       </c>
       <c r="C578" s="1">
-        <v>-0.058383453637361526</v>
+        <v>-0.24446198344230652</v>
       </c>
     </row>
     <row r="579">
@@ -6436,7 +6434,7 @@
         <v>0.0091324793174862862</v>
       </c>
       <c r="C579" s="1">
-        <v>0.16786067187786102</v>
+        <v>0.090510644018650055</v>
       </c>
     </row>
     <row r="580">
@@ -6447,7 +6445,7 @@
         <v>0.027222190052270889</v>
       </c>
       <c r="C580" s="1">
-        <v>0.077916808426380157</v>
+        <v>0.01399912778288126</v>
       </c>
     </row>
     <row r="581">
@@ -6458,7 +6456,7 @@
         <v>0.020644115284085274</v>
       </c>
       <c r="C581" s="1">
-        <v>-0.30710765719413757</v>
+        <v>-0.25441631674766541</v>
       </c>
     </row>
     <row r="582">
@@ -6469,7 +6467,7 @@
         <v>-0.097213059663772583</v>
       </c>
       <c r="C582" s="1">
-        <v>0.13579981029033661</v>
+        <v>0.09091418981552124</v>
       </c>
     </row>
     <row r="583">
@@ -6480,7 +6478,7 @@
         <v>0.054082661867141724</v>
       </c>
       <c r="C583" s="1">
-        <v>-0.6596793532371521</v>
+        <v>-0.53696542978286743</v>
       </c>
     </row>
     <row r="584">
@@ -6491,7 +6489,7 @@
         <v>0.057371694594621658</v>
       </c>
       <c r="C584" s="1">
-        <v>-0.3048553466796875</v>
+        <v>-0.23823484778404236</v>
       </c>
     </row>
     <row r="585">
@@ -6499,10 +6497,10 @@
         <v>202308</v>
       </c>
       <c r="B585" s="1">
-        <v>-0.22987088561058044</v>
+        <v>-0.22987088561058045</v>
       </c>
       <c r="C585" s="1">
-        <v>-0.012913254089653492</v>
+        <v>-0.042513255029916763</v>
       </c>
     </row>
     <row r="586">
@@ -6513,7 +6511,7 @@
         <v>-0.27043572068214417</v>
       </c>
       <c r="C586" s="1">
-        <v>-0.39734464883804321</v>
+        <v>-0.30441051721572876</v>
       </c>
     </row>
     <row r="587">
@@ -6524,7 +6522,7 @@
         <v>-0.29455530643463135</v>
       </c>
       <c r="C587" s="1">
-        <v>0.070154391229152679</v>
+        <v>0.047018911689519882</v>
       </c>
     </row>
     <row r="588">
@@ -6535,7 +6533,7 @@
         <v>0.38024553656578064</v>
       </c>
       <c r="C588" s="1">
-        <v>-0.12817969918251038</v>
+        <v>-0.1519743949174881</v>
       </c>
     </row>
     <row r="589">
@@ -6546,7 +6544,7 @@
         <v>0.10341822355985641</v>
       </c>
       <c r="C589" s="1">
-        <v>-0.7120169997215271</v>
+        <v>-0.52263975143432617</v>
       </c>
     </row>
   </sheetData>
